--- a/assets/xlsx/cards.unified.xlsx
+++ b/assets/xlsx/cards.unified.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF463"/>
+  <dimension ref="A1:AF464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>工商联</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -7429,37 +7429,47 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>北京市政协</t>
+          <t>中华全国工商业联合会</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议北京市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>工商联是中国共产党领导的以民营企业和民营经济人士为主体，具有统战性、经济性、民间性有机统一基本特征的人民团体和商会组织，是党和政府联系民营经济人士的桥梁纽带，是政府管理和服务民营经济的助手，是中国人民政治协商会议的重要组成部分。工商联工作是党的统一战线工作和经济工作的重要组成部分。工商联事业是党和国家事业的重要组成部分。</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>正省级政协,北京市,直辖市政协</t>
+          <t>全国工商联</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>访问官网 - www.bjzx.gov.cn</t>
+          <t>访问官网 - www.acfic.org.cn</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>https://www.bjzx.gov.cn</t>
+          <t>https://www.acfic.org.cn/</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>简介</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>https://www.acfic.org.cn/bhjj/gk/jj/</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -7489,37 +7499,37 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>天津市政协</t>
+          <t>北京市政协</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议天津市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议北京市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>正省级政协,天津市,直辖市政协</t>
+          <t>正省级政协,北京市,直辖市政协</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>访问官网 - www.tjszx.gov.cn</t>
+          <t>访问官网 - www.bjzx.gov.cn</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>https://www.tjszx.gov.cn</t>
+          <t>https://www.bjzx.gov.cn</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -7549,37 +7559,37 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>河北省政协</t>
+          <t>天津市政协</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议河北省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议天津市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>正省级政协,河北省,省政协</t>
+          <t>正省级政协,天津市,直辖市政协</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>访问官网 - www.hebzx.gov.cn</t>
+          <t>访问官网 - www.tjszx.gov.cn</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>https://www.hebzx.gov.cn</t>
+          <t>https://www.tjszx.gov.cn</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -7609,37 +7619,37 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>山西省政协</t>
+          <t>河北省政协</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议山西省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议河北省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>正省级政协,山西省,省政协</t>
+          <t>正省级政协,河北省,省政协</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>访问官网 - www.shanxizx.gov.cn</t>
+          <t>访问官网 - www.hebzx.gov.cn</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>https://www.shanxizx.gov.cn</t>
+          <t>https://www.hebzx.gov.cn</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -7669,42 +7679,37 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>内蒙古自治区政协</t>
+          <t>山西省政协</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议内蒙古自治区委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>http://www.nmgzx.gov.cn/favicon.ico</t>
+          <t>中国人民政治协商会议山西省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>正省级政协,内蒙古自治区,自治区政协</t>
+          <t>正省级政协,山西省,省政协</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>访问官网 - www.nmgzx.gov.cn</t>
+          <t>访问官网 - www.shanxizx.gov.cn</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>https://www.nmgzx.gov.cn</t>
+          <t>https://www.shanxizx.gov.cn</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -7734,37 +7739,42 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>辽宁省政协</t>
+          <t>内蒙古自治区政协</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议辽宁省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议内蒙古自治区委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>http://www.nmgzx.gov.cn/favicon.ico</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>正省级政协,辽宁省,省政协</t>
+          <t>正省级政协,内蒙古自治区,自治区政协</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>访问官网 - www.lnzx.gov.cn</t>
+          <t>访问官网 - www.nmgzx.gov.cn</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>https://www.lnzx.gov.cn</t>
+          <t>https://www.nmgzx.gov.cn</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -7794,37 +7804,37 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>吉林省政协</t>
+          <t>辽宁省政协</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议吉林省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议辽宁省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>正省级政协,吉林省,省政协</t>
+          <t>正省级政协,辽宁省,省政协</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>访问官网 - www.jlzx.gov.cn</t>
+          <t>访问官网 - www.lnzx.gov.cn</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>https://www.jlzx.gov.cn</t>
+          <t>https://www.lnzx.gov.cn</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -7854,37 +7864,37 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>黑龙江省政协</t>
+          <t>吉林省政协</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议黑龙江省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议吉林省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>正省级政协,黑龙江省,省政协</t>
+          <t>正省级政协,吉林省,省政协</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>访问官网 - www.hljzx.gov.cn</t>
+          <t>访问官网 - www.jlzx.gov.cn</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>https://www.hljzx.gov.cn</t>
+          <t>https://www.jlzx.gov.cn</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -7914,37 +7924,37 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>上海市政协</t>
+          <t>黑龙江省政协</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议上海市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议黑龙江省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>正省级政协,上海市,直辖市政协</t>
+          <t>正省级政协,黑龙江省,省政协</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>访问官网 - www.shszx.gov.cn</t>
+          <t>访问官网 - www.hljzx.gov.cn</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>https://www.shszx.gov.cn</t>
+          <t>https://www.hljzx.gov.cn</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -7974,37 +7984,37 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>江苏省政协</t>
+          <t>上海市政协</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议江苏省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议上海市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>正省级政协,江苏省,省政协</t>
+          <t>正省级政协,上海市,直辖市政协</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>访问官网 - www.jszx.gov.cn</t>
+          <t>访问官网 - www.shszx.gov.cn</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>https://www.jszx.gov.cn</t>
+          <t>https://www.shszx.gov.cn</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -8034,37 +8044,37 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>浙江省政协</t>
+          <t>江苏省政协</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议浙江省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议江苏省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>正省级政协,浙江省,省政协</t>
+          <t>正省级政协,江苏省,省政协</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>访问官网 - www.zjzx.gov.cn</t>
+          <t>访问官网 - www.jszx.gov.cn</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>https://www.zjzx.gov.cn</t>
+          <t>https://www.jszx.gov.cn</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -8094,37 +8104,37 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>安徽省政协</t>
+          <t>浙江省政协</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议安徽省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议浙江省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>正省级政协,安徽省,省政协</t>
+          <t>正省级政协,浙江省,省政协</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>访问官网 - www.ahzx.gov.cn</t>
+          <t>访问官网 - www.zjzx.gov.cn</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>https://www.ahzx.gov.cn</t>
+          <t>https://www.zjzx.gov.cn</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -8154,37 +8164,37 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>福建省政协</t>
+          <t>安徽省政协</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议福建省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议安徽省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>正省级政协,福建省,省政协</t>
+          <t>正省级政协,安徽省,省政协</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>访问官网 - www.fjzx.gov.cn</t>
+          <t>访问官网 - www.ahzx.gov.cn</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>https://www.fjzx.gov.cn</t>
+          <t>https://www.ahzx.gov.cn</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -8214,37 +8224,37 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>江西省政协</t>
+          <t>福建省政协</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议江西省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议福建省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>正省级政协,江西省,省政协</t>
+          <t>正省级政协,福建省,省政协</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>访问官网 - jxzx.jxnews.com.cn</t>
+          <t>访问官网 - www.fjzx.gov.cn</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>https://jxzx.jxnews.com.cn</t>
+          <t>https://www.fjzx.gov.cn</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -8274,37 +8284,37 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>山东省政协</t>
+          <t>江西省政协</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议山东省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议江西省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>正省级政协,山东省,省政协</t>
+          <t>正省级政协,江西省,省政协</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>访问官网 - www.sdzx.gov.cn</t>
+          <t>访问官网 - jxzx.jxnews.com.cn</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>https://www.sdzx.gov.cn</t>
+          <t>https://jxzx.jxnews.com.cn</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -8334,42 +8344,37 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>河南省政协</t>
+          <t>山东省政协</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议河南省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>https://www.google.com/s2/favicons?domain=http://www.hnzx.gov.cn/</t>
+          <t>中国人民政治协商会议山东省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>正省级政协,河南省,省政协</t>
+          <t>正省级政协,山东省,省政协</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>访问官网 - www.hnzx.gov.cn</t>
+          <t>访问官网 - www.sdzx.gov.cn</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>https://www.hnzx.gov.cn</t>
+          <t>https://www.sdzx.gov.cn</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -8399,42 +8404,42 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>湖北省政协</t>
+          <t>河南省政协</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议湖北省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议河南省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.hbzx.gov.cn/favicon.ico</t>
+          <t>https://www.google.com/s2/favicons?domain=http://www.hnzx.gov.cn/</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>正省级政协,湖北省,省政协</t>
+          <t>正省级政协,河南省,省政协</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>访问官网 - www.hbzx.gov.cn</t>
+          <t>访问官网 - www.hnzx.gov.cn</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>https://www.hbzx.gov.cn</t>
+          <t>https://www.hnzx.gov.cn</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -8464,37 +8469,42 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>湖南省政协</t>
+          <t>湖北省政协</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议湖南省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议湖北省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://www.hbzx.gov.cn/favicon.ico</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>正省级政协,湖南省,省政协</t>
+          <t>正省级政协,湖北省,省政协</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>访问官网 - www.hunanzx.gov.cn</t>
+          <t>访问官网 - www.hbzx.gov.cn</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>https://www.hunanzx.gov.cn</t>
+          <t>https://www.hbzx.gov.cn</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -8524,37 +8534,37 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>广东省政协</t>
+          <t>湖南省政协</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议广东省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议湖南省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>正省级政协,广东省,省政协</t>
+          <t>正省级政协,湖南省,省政协</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>访问官网 - www.gdzxb.gov.cn</t>
+          <t>访问官网 - www.hunanzx.gov.cn</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>https://www.gdzxb.gov.cn</t>
+          <t>https://www.hunanzx.gov.cn</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -8584,37 +8594,37 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>广西壮族自治区政协</t>
+          <t>广东省政协</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议广西壮族自治区委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议广东省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>正省级政协,广西壮族自治区,自治区政协</t>
+          <t>正省级政协,广东省,省政协</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>访问官网 - www.gxzx.gov.cn</t>
+          <t>访问官网 - www.gdzxb.gov.cn</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>https://www.gxzx.gov.cn</t>
+          <t>https://www.gdzxb.gov.cn</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -8644,37 +8654,37 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>海南省政协</t>
+          <t>广西壮族自治区政协</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议海南省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议广西壮族自治区委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>正省级政协,海南省,省政协</t>
+          <t>正省级政协,广西壮族自治区,自治区政协</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>访问官网 - www.hainanzx.gov.cn</t>
+          <t>访问官网 - www.gxzx.gov.cn</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>https://www.hainanzx.gov.cn</t>
+          <t>https://www.gxzx.gov.cn</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -8704,37 +8714,37 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>重庆市政协</t>
+          <t>海南省政协</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议重庆市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议海南省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>正省级政协,重庆市,直辖市政协</t>
+          <t>正省级政协,海南省,省政协</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>访问官网 - www.cqzx.gov.cn</t>
+          <t>访问官网 - www.hainanzx.gov.cn</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>https://www.cqzx.gov.cn</t>
+          <t>https://www.hainanzx.gov.cn</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -8764,37 +8774,37 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>四川省政协</t>
+          <t>重庆市政协</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议四川省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议重庆市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>正省级政协,四川省,省政协</t>
+          <t>正省级政协,重庆市,直辖市政协</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>访问官网 - www.sczx.gov.cn</t>
+          <t>访问官网 - www.cqzx.gov.cn</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>https://www.sczx.gov.cn</t>
+          <t>https://www.cqzx.gov.cn</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -8824,37 +8834,37 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>贵州省政协</t>
+          <t>四川省政协</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议贵州省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议四川省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>正省级政协,贵州省,省政协</t>
+          <t>正省级政协,四川省,省政协</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>访问官网 - www.gzszx.gov.cn</t>
+          <t>访问官网 - www.sczx.gov.cn</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>https://www.gzszx.gov.cn</t>
+          <t>https://www.sczx.gov.cn</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -8884,37 +8894,37 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>云南省政协</t>
+          <t>贵州省政协</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议云南省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议贵州省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>正省级政协,云南省,省政协</t>
+          <t>正省级政协,贵州省,省政协</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>访问官网 - www.ynzx.gov.cn</t>
+          <t>访问官网 - www.gzszx.gov.cn</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>https://www.ynzx.gov.cn</t>
+          <t>https://www.gzszx.gov.cn</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -8944,37 +8954,37 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>西藏自治区政协</t>
+          <t>云南省政协</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议西藏自治区委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议云南省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>正省级政协,西藏自治区,自治区政协</t>
+          <t>正省级政协,云南省,省政协</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>访问官网 - www.xizangzx.gov.cn</t>
+          <t>访问官网 - www.ynzx.gov.cn</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>https://www.xizangzx.gov.cn</t>
+          <t>https://www.ynzx.gov.cn</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -9004,37 +9014,37 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>陕西省政协</t>
+          <t>西藏自治区政协</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议陕西省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议西藏自治区委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>正省级政协,陕西省,省政协</t>
+          <t>正省级政协,西藏自治区,自治区政协</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>54</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>访问官网 - www.sxzx.gov.cn</t>
+          <t>访问官网 - www.xizangzx.gov.cn</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>https://www.sxzx.gov.cn</t>
+          <t>https://www.xizangzx.gov.cn</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -9064,37 +9074,37 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>甘肃省政协</t>
+          <t>陕西省政协</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议甘肃省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议陕西省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>正省级政协,甘肃省,省政协</t>
+          <t>正省级政协,陕西省,省政协</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>访问官网 - www.gszx.gov.cn</t>
+          <t>访问官网 - www.sxzx.gov.cn</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>https://www.gszx.gov.cn</t>
+          <t>https://www.sxzx.gov.cn</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
@@ -9124,37 +9134,37 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>青海省政协</t>
+          <t>甘肃省政协</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议青海省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议甘肃省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>正省级政协,青海省,省政协</t>
+          <t>正省级政协,甘肃省,省政协</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>访问官网 - www.qhszx.gov.cn</t>
+          <t>访问官网 - www.gszx.gov.cn</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>https://www.qhszx.gov.cn</t>
+          <t>https://www.gszx.gov.cn</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -9184,37 +9194,37 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>宁夏回族自治区政协</t>
+          <t>青海省政协</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议宁夏回族自治区委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议青海省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>正省级政协,宁夏回族自治区,自治区政协</t>
+          <t>正省级政协,青海省,省政协</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>访问官网 - www.nxzx.gov.cn</t>
+          <t>访问官网 - www.qhszx.gov.cn</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>https://www.nxzx.gov.cn</t>
+          <t>https://www.qhszx.gov.cn</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -9244,37 +9254,37 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区政协</t>
+          <t>宁夏回族自治区政协</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议新疆维吾尔自治区委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议宁夏回族自治区委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>正省级政协,新疆维吾尔自治区,自治区政协</t>
+          <t>正省级政协,宁夏回族自治区,自治区政协</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>访问官网 - www.xjzx.gov.cn</t>
+          <t>访问官网 - www.nxzx.gov.cn</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>https://www.xjzx.gov.cn</t>
+          <t>https://www.nxzx.gov.cn</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -9304,32 +9314,37 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>广州市政协</t>
+          <t>新疆维吾尔自治区政协</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议广州市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>https://www.gzzx.gov.cn/images/iconcf134.ico</t>
+          <t>中国人民政治协商会议新疆维吾尔自治区委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>副省级政协,广州市,市政协,广东省,省会城市</t>
+          <t>正省级政协,新疆维吾尔自治区,自治区政协</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>65</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>访问官网 - www.gzzx.gov.cn</t>
+          <t>访问官网 - www.xjzx.gov.cn</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>https://www.gzzx.gov.cn</t>
+          <t>https://www.xjzx.gov.cn</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -9359,27 +9374,32 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>深圳市政协</t>
+          <t>广州市政协</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议深圳市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议广州市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://www.gzzx.gov.cn/images/iconcf134.ico</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>副省级政协,深圳市,市政协,广东省,计划单市</t>
+          <t>副省级政协,广州市,市政协,广东省,省会城市</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>访问官网 - www.szzx.gov.cn</t>
+          <t>访问官网 - www.gzzx.gov.cn</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>https://www.szzx.gov.cn/</t>
+          <t>https://www.gzzx.gov.cn</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -9409,27 +9429,27 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>珠海市政协</t>
+          <t>深圳市政协</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议珠海市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议深圳市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>地级政协,珠海市,市政协,广东省</t>
+          <t>副省级政协,深圳市,市政协,广东省,计划单市</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>访问官网 - www.zhzx.gov.cn</t>
+          <t>访问官网 - www.szzx.gov.cn</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>https://www.zhzx.gov.cn/</t>
+          <t>https://www.szzx.gov.cn/</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -9459,27 +9479,27 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>汕头市政协</t>
+          <t>珠海市政协</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议汕头市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议珠海市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>地级政协,汕头市,市政协,广东省</t>
+          <t>地级政协,珠海市,市政协,广东省</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>访问官网 - stzx.shantou.gov.cn</t>
+          <t>访问官网 - www.zhzx.gov.cn</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>https://stzx.shantou.gov.cn/</t>
+          <t>https://www.zhzx.gov.cn/</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -9509,32 +9529,27 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>汕头市金平区政协</t>
+          <t>汕头市政协</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议汕头市金平区委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>http://www.jpzx.gov.cn/favicon.ico</t>
+          <t>中国人民政治协商会议汕头市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>县级政协,汕头市金平区,市辖区政协,广东省</t>
+          <t>地级政协,汕头市,市政协,广东省</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>访问官网 - www.jpzx.gov.cn</t>
+          <t>访问官网 - stzx.shantou.gov.cn</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>https://www.jpzx.gov.cn/welcome</t>
+          <t>https://stzx.shantou.gov.cn/</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -9564,27 +9579,32 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>佛山市政协</t>
+          <t>汕头市金平区政协</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议佛山市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议汕头市金平区委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>http://www.jpzx.gov.cn/favicon.ico</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>地级政协,佛山市,市政协,广东省</t>
+          <t>县级政协,汕头市金平区,市辖区政协,广东省</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>访问官网 - www.fszx.gov.cn</t>
+          <t>访问官网 - www.jpzx.gov.cn</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>https://www.fszx.gov.cn/</t>
+          <t>https://www.jpzx.gov.cn/welcome</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -9614,27 +9634,27 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>韶关市政协</t>
+          <t>佛山市政协</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议韶关市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议佛山市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>地级政协,韶关市,市政协,广东省</t>
+          <t>地级政协,佛山市,市政协,广东省</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>访问官网 - www.sgzxb.gov.cn</t>
+          <t>访问官网 - www.fszx.gov.cn</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>https://www.sgzxb.gov.cn/</t>
+          <t>https://www.fszx.gov.cn/</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr">
@@ -9664,27 +9684,27 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>河源市政协</t>
+          <t>韶关市政协</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议河源市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议韶关市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>地级政协,河源市,市政协,广东省</t>
+          <t>地级政协,韶关市,市政协,广东省</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>访问官网 - www.gdhyzx.gov.cn</t>
+          <t>访问官网 - www.sgzxb.gov.cn</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>https://www.gdhyzx.gov.cn/hyzx/index.html</t>
+          <t>https://www.sgzxb.gov.cn/</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -9714,27 +9734,27 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>梅州市政协</t>
+          <t>河源市政协</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议梅州市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议河源市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>地级政协,梅州市,市政协,广东省</t>
+          <t>地级政协,河源市,市政协,广东省</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>访问官网 - www.mzzx.gov.cn</t>
+          <t>访问官网 - www.gdhyzx.gov.cn</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>https://www.mzzx.gov.cn/</t>
+          <t>https://www.gdhyzx.gov.cn/hyzx/index.html</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
@@ -9764,27 +9784,27 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>惠州市政协</t>
+          <t>梅州市政协</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议惠州市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议梅州市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>地级政协,惠州市,市政协,广东省</t>
+          <t>地级政协,梅州市,市政协,广东省</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>访问官网 - zx.huizhou.gov.cn</t>
+          <t>访问官网 - www.mzzx.gov.cn</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>https://zx.huizhou.gov.cn/</t>
+          <t>https://www.mzzx.gov.cn/</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
@@ -9814,27 +9834,27 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>汕尾市政协</t>
+          <t>惠州市政协</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议汕尾市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议惠州市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>地级政协,汕尾市,市政协,广东省</t>
+          <t>地级政协,惠州市,市政协,广东省</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>访问官网 - www.swzx.gov.cn</t>
+          <t>访问官网 - zx.huizhou.gov.cn</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>https://www.swzx.gov.cn/</t>
+          <t>https://zx.huizhou.gov.cn/</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -9864,27 +9884,27 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>东莞市政协</t>
+          <t>汕尾市政协</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议东莞市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议汕尾市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>地级政协,东莞市,市政协,广东省</t>
+          <t>地级政协,汕尾市,市政协,广东省</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>访问官网 - dgzx.dg.gov.cn</t>
+          <t>访问官网 - www.swzx.gov.cn</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>https://dgzx.dg.gov.cn/</t>
+          <t>https://www.swzx.gov.cn/</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -9914,27 +9934,27 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>中山市政协</t>
+          <t>东莞市政协</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议中山市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议东莞市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>地级政协,中山市,市政协,广东省</t>
+          <t>地级政协,东莞市,市政协,广东省</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>访问官网 - zszx.zsnews.cn</t>
+          <t>访问官网 - dgzx.dg.gov.cn</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>https://zszx.zsnews.cn/</t>
+          <t>https://dgzx.dg.gov.cn/</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -9964,27 +9984,27 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>江门市政协</t>
+          <t>中山市政协</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议江门市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议中山市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>地级政协,江门市,市政协,广东省</t>
+          <t>地级政协,中山市,市政协,广东省</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>访问官网 - zx.jiangmen.cn</t>
+          <t>访问官网 - zszx.zsnews.cn</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>https://zx.jiangmen.cn/</t>
+          <t>https://zszx.zsnews.cn/</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -10014,27 +10034,27 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>阳江市政协</t>
+          <t>江门市政协</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议阳江市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议江门市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>地级政协,阳江市,市政协,广东省</t>
+          <t>地级政协,江门市,市政协,广东省</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>访问官网 - www.yjszx.gov.cn</t>
+          <t>访问官网 - zx.jiangmen.cn</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>https://www.yjszx.gov.cn/default.html</t>
+          <t>https://zx.jiangmen.cn/</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -10064,32 +10084,27 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>湛江市政协</t>
+          <t>阳江市政协</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议湛江市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/</t>
+          <t>中国人民政治协商会议阳江市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>地级政协,湛江市,市政协,广东省</t>
+          <t>地级政协,阳江市,市政协,广东省</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>访问官网 - www.gdzjzx.gov.cn</t>
+          <t>访问官网 - www.yjszx.gov.cn</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>https://www.gdzjzx.gov.cn/</t>
+          <t>https://www.yjszx.gov.cn/default.html</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
@@ -10119,27 +10134,32 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>茂名市政协</t>
+          <t>湛江市政协</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议茂名市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议湛江市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>地级政协,茂名市,市政协,广东省</t>
+          <t>地级政协,湛江市,市政协,广东省</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>访问官网 - zx.maoming.gov.cn</t>
+          <t>访问官网 - www.gdzjzx.gov.cn</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>https://zx.maoming.gov.cn/website/main/jsp/index.jsp</t>
+          <t>https://www.gdzjzx.gov.cn/</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -10169,27 +10189,27 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>肇庆市政协</t>
+          <t>茂名市政协</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议肇庆市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议茂名市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>地级政协,肇庆市,市政协,广东省</t>
+          <t>地级政协,茂名市,市政协,广东省</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>访问官网 - zqzx.gov.cn</t>
+          <t>访问官网 - zx.maoming.gov.cn</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>https://zqzx.gov.cn/index.html</t>
+          <t>https://zx.maoming.gov.cn/website/main/jsp/index.jsp</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -10219,27 +10239,27 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>潮州市政协</t>
+          <t>肇庆市政协</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议潮州市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议肇庆市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>地级政协,潮州市,市政协,广东省</t>
+          <t>地级政协,肇庆市,市政协,广东省</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>访问官网 - czzx.gov.cn</t>
+          <t>访问官网 - zqzx.gov.cn</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>https://czzx.gov.cn/</t>
+          <t>https://zqzx.gov.cn/index.html</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -10269,27 +10289,27 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>揭阳市政协</t>
+          <t>潮州市政协</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议揭阳市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议潮州市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>地级政协,揭阳市,市政协,广东省</t>
+          <t>地级政协,潮州市,市政协,广东省</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>访问官网 - www.jieyangzhengxie.gov.cn/</t>
+          <t>访问官网 - czzx.gov.cn</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.jieyangzhengxie.gov.cn/ </t>
+          <t>https://czzx.gov.cn/</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -10319,27 +10339,27 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>云浮市政协</t>
+          <t>揭阳市政协</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议云浮市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议揭阳市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>地级政协,云浮市,市政协,广东省</t>
+          <t>地级政协,揭阳市,市政协,广东省</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>访问官网 - zx.yunfu.gov.cn</t>
+          <t>访问官网 - www.jieyangzhengxie.gov.cn/</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>https://zx.yunfu.gov.cn/</t>
+          <t xml:space="preserve">https://www.jieyangzhengxie.gov.cn/ </t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -10369,27 +10389,27 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>哈尔滨市政协</t>
+          <t>云浮市政协</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议哈尔滨市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议云浮市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>副省级政协,哈尔滨市,市政协,黑龙江省,省会城市</t>
+          <t>地级政协,云浮市,市政协,广东省</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>访问官网 - www.hrbzx.gov.cn</t>
+          <t>访问官网 - zx.yunfu.gov.cn</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>https://www.hrbzx.gov.cn/</t>
+          <t>https://zx.yunfu.gov.cn/</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
@@ -10419,27 +10439,27 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>武汉市政协</t>
+          <t>哈尔滨市政协</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议武汉市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议哈尔滨市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>副省级政协,武汉市,市政协,湖北省,省会城市</t>
+          <t>副省级政协,哈尔滨市,市政协,黑龙江省,省会城市</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>访问官网 - www.whzx.org.cn</t>
+          <t>访问官网 - www.hrbzx.gov.cn</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.whzx.org.cn/  </t>
+          <t>https://www.hrbzx.gov.cn/</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -10461,50 +10481,35 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>中央网信办（国家互联网信息办公室）违法和不良信息举报中心</t>
+          <t>武汉市政协</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>统筹协调全国互联网违法和不良信息举报工作；指导、监督各地各网站规范开展互联网违法和不良信息举报工作；受理、协助处置网民对互联网违法和不良信息的举报；宣传动员广大网民积极参与互联网违法和不良信息举报监督；主办中国互联网联合辟谣平台，统筹做好网络辟谣工作；开展国际交流合作，加强与境外国际组织、相关机构、互联网企业的联系，协调处理相关有害信息。</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>https://zhengxie.com.cn/assets/images/12377-3-04.webp</t>
+          <t>中国人民政治协商会议武汉市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>举报中心</t>
+          <t>副省级政协,武汉市,市政协,湖北省,省会城市</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>访问官网</t>
+          <t>访问官网 - www.whzx.org.cn</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>https://www.12377.cn</t>
-        </is>
-      </c>
-      <c r="N191" t="inlineStr">
-        <is>
-          <t>机构简介</t>
-        </is>
-      </c>
-      <c r="O191" t="inlineStr">
-        <is>
-          <t>https://www.12377.cn/jgjj.html?tab=5</t>
+          <t xml:space="preserve">https://www.whzx.org.cn/  </t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
@@ -10530,21 +10535,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>12321网络不良与垃圾信息举报受理中心</t>
+          <t>中央网信办（国家互联网信息办公室）违法和不良信息举报中心</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>中国互联网协会受工业和信息化部委托设立的投诉受理机构。负责协助工业和信息化部承担关于互联网、移动电话网、固定电话网等各种形式信息通信网络及电信业务中不良与垃圾信息的投诉受理、线索转办及信息统计等工作。</t>
+          <t>统筹协调全国互联网违法和不良信息举报工作；指导、监督各地各网站规范开展互联网违法和不良信息举报工作；受理、协助处置网民对互联网违法和不良信息的举报；宣传动员广大网民积极参与互联网违法和不良信息举报监督；主办中国互联网联合辟谣平台，统筹做好网络辟谣工作；开展国际交流合作，加强与境外国际组织、相关机构、互联网企业的联系，协调处理相关有害信息。</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://www.12321.cn/Public/home/image/favicon.ico,#FFFFFF</t>
+          <t>https://zhengxie.com.cn/assets/images/12377-3-04.webp</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -10559,17 +10564,17 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>https://www.12321.cn</t>
+          <t>https://www.12377.cn</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>机构介绍</t>
+          <t>机构简介</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>https://www.12321.cn/single?tpl=institution</t>
+          <t>https://www.12377.cn/jgjj.html?tab=5</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -10591,7 +10596,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E193" t="n">
@@ -10599,12 +10604,42 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>沈阳市政协</t>
+          <t>12321网络不良与垃圾信息举报受理中心</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>中国互联网协会受工业和信息化部委托设立的投诉受理机构。负责协助工业和信息化部承担关于互联网、移动电话网、固定电话网等各种形式信息通信网络及电信业务中不良与垃圾信息的投诉受理、线索转办及信息统计等工作。</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>https://www.12321.cn/Public/home/image/favicon.ico,#FFFFFF</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>副省级政协,沈阳市,市政协,辽宁省,省会城市</t>
+          <t>举报中心</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>访问官网</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>https://www.12321.cn</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>机构介绍</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>https://www.12321.cn/single?tpl=institution</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
@@ -10634,12 +10669,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>成都市政协</t>
+          <t>沈阳市政协</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>副省级政协,成都市,市政协,四川省,省会城市</t>
+          <t>副省级政协,沈阳市,市政协,辽宁省,省会城市</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -10669,12 +10704,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>南京市政协</t>
+          <t>成都市政协</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>副省级政协,南京市,市政协,江苏省,省会城市</t>
+          <t>副省级政协,成都市,市政协,四川省,省会城市</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -10704,12 +10739,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>西安市政协</t>
+          <t>南京市政协</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>副省级政协,西安市,市政协,陕西省,省会城市</t>
+          <t>副省级政协,南京市,市政协,江苏省,省会城市</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -10739,12 +10774,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>长春市政协</t>
+          <t>西安市政协</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>副省级政协,长春市,市政协,吉林省,省会城市</t>
+          <t>副省级政协,西安市,市政协,陕西省,省会城市</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -10774,12 +10809,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>济南市政协</t>
+          <t>长春市政协</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>副省级政协,济南市,市政协,山东省,省会城市</t>
+          <t>副省级政协,长春市,市政协,吉林省,省会城市</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -10809,12 +10844,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>杭州市政协</t>
+          <t>济南市政协</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>副省级政协,杭州市,市政协,浙江省,省会城市</t>
+          <t>副省级政协,济南市,市政协,山东省,省会城市</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -10844,12 +10879,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>大连市政协</t>
+          <t>杭州市政协</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>副省级政协,大连市,市政协,辽宁省,计划单列市</t>
+          <t>副省级政协,杭州市,市政协,浙江省,省会城市</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
@@ -10879,12 +10914,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>青岛市政协</t>
+          <t>大连市政协</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>副省级政协,青岛市,市政协,山东省,计划单列市</t>
+          <t>副省级政协,大连市,市政协,辽宁省,计划单列市</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -10914,12 +10949,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>厦门市政协</t>
+          <t>青岛市政协</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>副省级政协,厦门市,市政协,福建省,计划单列市</t>
+          <t>副省级政协,青岛市,市政协,山东省,计划单列市</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -10949,12 +10984,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>宁波市政协</t>
+          <t>厦门市政协</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>副省级政协,宁波市,市政协,浙江省,计划单列市</t>
+          <t>副省级政协,厦门市,市政协,福建省,计划单列市</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -10984,12 +11019,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>清远市政协</t>
+          <t>宁波市政协</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>地级政协,清远市,市政协,广东省</t>
+          <t>副省级政协,宁波市,市政协,浙江省,计划单列市</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -11019,12 +11054,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>石家庄市政协</t>
+          <t>清远市政协</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>地级政协,石家庄市,市政协,河北省</t>
+          <t>地级政协,清远市,市政协,广东省</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -11054,12 +11089,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>唐山市政协</t>
+          <t>石家庄市政协</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>地级政协,唐山市,市政协,河北省</t>
+          <t>地级政协,石家庄市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -11089,12 +11124,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>秦皇岛市政协</t>
+          <t>唐山市政协</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>地级政协,秦皇岛市,市政协,河北省</t>
+          <t>地级政协,唐山市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -11124,12 +11159,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>邯郸市政协</t>
+          <t>秦皇岛市政协</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>地级政协,邯郸市,市政协,河北省</t>
+          <t>地级政协,秦皇岛市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -11159,12 +11194,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>邢台市政协</t>
+          <t>邯郸市政协</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>地级政协,邢台市,市政协,河北省</t>
+          <t>地级政协,邯郸市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -11194,12 +11229,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>保定市政协</t>
+          <t>邢台市政协</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>地级政协,保定市,市政协,河北省</t>
+          <t>地级政协,邢台市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -11229,12 +11264,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>张家口市政协</t>
+          <t>保定市政协</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>地级政协,张家口市,市政协,河北省</t>
+          <t>地级政协,保定市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -11264,12 +11299,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>承德市政协</t>
+          <t>张家口市政协</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>地级政协,承德市,市政协,河北省</t>
+          <t>地级政协,张家口市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -11299,12 +11334,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>沧州市政协</t>
+          <t>承德市政协</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>地级政协,沧州市,市政协,河北省</t>
+          <t>地级政协,承德市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -11334,12 +11369,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>廊坊市政协</t>
+          <t>沧州市政协</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>地级政协,廊坊市,市政协,河北省</t>
+          <t>地级政协,沧州市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -11369,12 +11404,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>衡水市政协</t>
+          <t>廊坊市政协</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>地级政协,衡水市,市政协,河北省</t>
+          <t>地级政协,廊坊市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -11404,12 +11439,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>太原市政协</t>
+          <t>衡水市政协</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>地级政协,太原市,市政协,山西省</t>
+          <t>地级政协,衡水市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -11439,12 +11474,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>大同市政协</t>
+          <t>太原市政协</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>地级政协,大同市,市政协,山西省</t>
+          <t>地级政协,太原市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -11474,12 +11509,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>阳泉市政协</t>
+          <t>大同市政协</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>地级政协,阳泉市,市政协,山西省</t>
+          <t>地级政协,大同市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -11509,12 +11544,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>长治市政协</t>
+          <t>阳泉市政协</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>地级政协,长治市,市政协,山西省</t>
+          <t>地级政协,阳泉市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -11544,12 +11579,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>晋城市政协</t>
+          <t>长治市政协</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>地级政协,晋城市,市政协,山西省</t>
+          <t>地级政协,长治市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -11579,12 +11614,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>朔州市政协</t>
+          <t>晋城市政协</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>地级政协,朔州市,市政协,山西省</t>
+          <t>地级政协,晋城市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -11614,12 +11649,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>晋中市政协</t>
+          <t>朔州市政协</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>地级政协,晋中市,市政协,山西省</t>
+          <t>地级政协,朔州市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -11649,12 +11684,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>运城市政协</t>
+          <t>晋中市政协</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>地级政协,运城市,市政协,山西省</t>
+          <t>地级政协,晋中市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -11684,12 +11719,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>忻州市政协</t>
+          <t>运城市政协</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>地级政协,忻州市,市政协,山西省</t>
+          <t>地级政协,运城市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -11719,12 +11754,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>临汾市政协</t>
+          <t>忻州市政协</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>地级政协,临汾市,市政协,山西省</t>
+          <t>地级政协,忻州市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -11754,12 +11789,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>吕梁市政协</t>
+          <t>临汾市政协</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>地级政协,吕梁市,市政协,山西省</t>
+          <t>地级政协,临汾市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -11789,12 +11824,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>呼和浩特市政协</t>
+          <t>吕梁市政协</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>地级政协,呼和浩特市,市政协,内蒙古自治区</t>
+          <t>地级政协,吕梁市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -11824,12 +11859,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>包头市政协</t>
+          <t>呼和浩特市政协</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>地级政协,包头市,市政协,内蒙古自治区</t>
+          <t>地级政协,呼和浩特市,市政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -11859,12 +11894,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>乌海市政协</t>
+          <t>包头市政协</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>地级政协,乌海市,市政协,内蒙古自治区</t>
+          <t>地级政协,包头市,市政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -11894,12 +11929,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>赤峰市政协</t>
+          <t>乌海市政协</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>地级政协,赤峰市,市政协,内蒙古自治区</t>
+          <t>地级政协,乌海市,市政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -11929,12 +11964,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>通辽市政协</t>
+          <t>赤峰市政协</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>地级政协,通辽市,市政协,内蒙古自治区</t>
+          <t>地级政协,赤峰市,市政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -11964,12 +11999,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>鄂尔多斯市政协</t>
+          <t>通辽市政协</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>地级政协,鄂尔多斯市,市政协,内蒙古自治区</t>
+          <t>地级政协,通辽市,市政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -11999,12 +12034,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>呼伦贝尔市政协</t>
+          <t>鄂尔多斯市政协</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>地级政协,呼伦贝尔市,市政协,内蒙古自治区</t>
+          <t>地级政协,鄂尔多斯市,市政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -12034,12 +12069,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>巴彦淖尔市政协</t>
+          <t>呼伦贝尔市政协</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>地级政协,巴彦淖尔市,市政协,内蒙古自治区</t>
+          <t>地级政协,呼伦贝尔市,市政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -12069,12 +12104,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>乌兰察布市政协</t>
+          <t>巴彦淖尔市政协</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>地级政协,乌兰察布市,市政协,内蒙古自治区</t>
+          <t>地级政协,巴彦淖尔市,市政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -12104,12 +12139,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>鞍山市政协</t>
+          <t>乌兰察布市政协</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>地级政协,鞍山市,市政协,辽宁省</t>
+          <t>地级政协,乌兰察布市,市政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -12139,12 +12174,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>抚顺市政协</t>
+          <t>鞍山市政协</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>地级政协,抚顺市,市政协,辽宁省</t>
+          <t>地级政协,鞍山市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -12174,12 +12209,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>本溪市政协</t>
+          <t>抚顺市政协</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>地级政协,本溪市,市政协,辽宁省</t>
+          <t>地级政协,抚顺市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -12209,12 +12244,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>丹东市政协</t>
+          <t>本溪市政协</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>地级政协,丹东市,市政协,辽宁省</t>
+          <t>地级政协,本溪市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -12244,12 +12279,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>锦州市政协</t>
+          <t>丹东市政协</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>地级政协,锦州市,市政协,辽宁省</t>
+          <t>地级政协,丹东市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -12279,12 +12314,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>营口市政协</t>
+          <t>锦州市政协</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>地级政协,营口市,市政协,辽宁省</t>
+          <t>地级政协,锦州市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
@@ -12314,12 +12349,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>阜新市政协</t>
+          <t>营口市政协</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>地级政协,阜新市,市政协,辽宁省</t>
+          <t>地级政协,营口市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -12349,12 +12384,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>辽阳市政协</t>
+          <t>阜新市政协</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>地级政协,辽阳市,市政协,辽宁省</t>
+          <t>地级政协,阜新市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -12384,12 +12419,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>盘锦市政协</t>
+          <t>辽阳市政协</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>地级政协,盘锦市,市政协,辽宁省</t>
+          <t>地级政协,辽阳市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
@@ -12419,12 +12454,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>铁岭市政协</t>
+          <t>盘锦市政协</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>地级政协,铁岭市,市政协,辽宁省</t>
+          <t>地级政协,盘锦市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -12454,12 +12489,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>朝阳市政协</t>
+          <t>铁岭市政协</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>地级政协,朝阳市,市政协,辽宁省</t>
+          <t>地级政协,铁岭市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -12489,12 +12524,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>葫芦岛市政协</t>
+          <t>朝阳市政协</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>地级政协,葫芦岛市,市政协,辽宁省</t>
+          <t>地级政协,朝阳市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -12524,12 +12559,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>吉林市政协</t>
+          <t>葫芦岛市政协</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>地级政协,吉林市,市政协,吉林省</t>
+          <t>地级政协,葫芦岛市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -12559,12 +12594,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>四平市政协</t>
+          <t>吉林市政协</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>地级政协,四平市,市政协,吉林省</t>
+          <t>地级政协,吉林市,市政协,吉林省</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
@@ -12594,12 +12629,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>辽源市政协</t>
+          <t>四平市政协</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>地级政协,辽源市,市政协,吉林省</t>
+          <t>地级政协,四平市,市政协,吉林省</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -12629,12 +12664,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>通化市政协</t>
+          <t>辽源市政协</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>地级政协,通化市,市政协,吉林省</t>
+          <t>地级政协,辽源市,市政协,吉林省</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -12664,12 +12699,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>白山市政协</t>
+          <t>通化市政协</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>地级政协,白山市,市政协,吉林省</t>
+          <t>地级政协,通化市,市政协,吉林省</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -12699,12 +12734,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>松原市政协</t>
+          <t>白山市政协</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>地级政协,松原市,市政协,吉林省</t>
+          <t>地级政协,白山市,市政协,吉林省</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -12734,12 +12769,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>白城市政协</t>
+          <t>松原市政协</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>地级政协,白城市,市政协,吉林省</t>
+          <t>地级政协,松原市,市政协,吉林省</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -12769,12 +12804,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>齐齐哈尔市政协</t>
+          <t>白城市政协</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>地级政协,齐齐哈尔市,市政协,黑龙江省</t>
+          <t>地级政协,白城市,市政协,吉林省</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -12804,12 +12839,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>鸡西市政协</t>
+          <t>齐齐哈尔市政协</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>地级政协,鸡西市,市政协,黑龙江省</t>
+          <t>地级政协,齐齐哈尔市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF256" t="inlineStr">
@@ -12839,12 +12874,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>鹤岗市政协</t>
+          <t>鸡西市政协</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>地级政协,鹤岗市,市政协,黑龙江省</t>
+          <t>地级政协,鸡西市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF257" t="inlineStr">
@@ -12874,12 +12909,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>双鸭山市政协</t>
+          <t>鹤岗市政协</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>地级政协,双鸭山市,市政协,黑龙江省</t>
+          <t>地级政协,鹤岗市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -12909,12 +12944,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>大庆市政协</t>
+          <t>双鸭山市政协</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>地级政协,大庆市,市政协,黑龙江省</t>
+          <t>地级政协,双鸭山市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF259" t="inlineStr">
@@ -12944,12 +12979,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>伊春市政协</t>
+          <t>大庆市政协</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>地级政协,伊春市,市政协,黑龙江省</t>
+          <t>地级政协,大庆市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -12979,12 +13014,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>佳木斯市政协</t>
+          <t>伊春市政协</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>地级政协,佳木斯市,市政协,黑龙江省</t>
+          <t>地级政协,伊春市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -13014,12 +13049,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>七台河市政协</t>
+          <t>佳木斯市政协</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>地级政协,七台河市,市政协,黑龙江省</t>
+          <t>地级政协,佳木斯市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
@@ -13049,12 +13084,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>牡丹江市政协</t>
+          <t>七台河市政协</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>地级政协,牡丹江市,市政协,黑龙江省</t>
+          <t>地级政协,七台河市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
@@ -13084,12 +13119,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>黑河市政协</t>
+          <t>牡丹江市政协</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>地级政协,黑河市,市政协,黑龙江省</t>
+          <t>地级政协,牡丹江市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -13119,12 +13154,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>绥化市政协</t>
+          <t>黑河市政协</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>地级政协,绥化市,市政协,黑龙江省</t>
+          <t>地级政协,黑河市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
@@ -13154,12 +13189,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>无锡市政协</t>
+          <t>绥化市政协</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>地级政协,无锡市,市政协,江苏省</t>
+          <t>地级政协,绥化市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -13189,12 +13224,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>徐州市政协</t>
+          <t>无锡市政协</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>地级政协,徐州市,市政协,江苏省</t>
+          <t>地级政协,无锡市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF267" t="inlineStr">
@@ -13224,12 +13259,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>常州市政协</t>
+          <t>徐州市政协</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>地级政协,常州市,市政协,江苏省</t>
+          <t>地级政协,徐州市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -13259,12 +13294,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>苏州市政协</t>
+          <t>常州市政协</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>地级政协,苏州市,市政协,江苏省</t>
+          <t>地级政协,常州市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -13294,12 +13329,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>南通市政协</t>
+          <t>苏州市政协</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>地级政协,南通市,市政协,江苏省</t>
+          <t>地级政协,苏州市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -13329,12 +13364,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>连云港市政协</t>
+          <t>南通市政协</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>地级政协,连云港市,市政协,江苏省</t>
+          <t>地级政协,南通市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -13364,12 +13399,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>淮安市政协</t>
+          <t>连云港市政协</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>地级政协,淮安市,市政协,江苏省</t>
+          <t>地级政协,连云港市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -13399,12 +13434,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>盐城市政协</t>
+          <t>淮安市政协</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>地级政协,盐城市,市政协,江苏省</t>
+          <t>地级政协,淮安市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -13434,12 +13469,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>扬州市政协</t>
+          <t>盐城市政协</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>地级政协,扬州市,市政协,江苏省</t>
+          <t>地级政协,盐城市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -13469,12 +13504,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>镇江市政协</t>
+          <t>扬州市政协</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>地级政协,镇江市,市政协,江苏省</t>
+          <t>地级政协,扬州市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -13504,12 +13539,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>泰州市政协</t>
+          <t>镇江市政协</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>地级政协,泰州市,市政协,江苏省</t>
+          <t>地级政协,镇江市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -13539,12 +13574,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>宿迁市政协</t>
+          <t>泰州市政协</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>地级政协,宿迁市,市政协,江苏省</t>
+          <t>地级政协,泰州市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -13574,12 +13609,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>温州市政协</t>
+          <t>宿迁市政协</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>地级政协,温州市,市政协,浙江省</t>
+          <t>地级政协,宿迁市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -13609,12 +13644,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>嘉兴市政协</t>
+          <t>温州市政协</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>地级政协,嘉兴市,市政协,浙江省</t>
+          <t>地级政协,温州市,市政协,浙江省</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -13644,12 +13679,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>湖州市政协</t>
+          <t>嘉兴市政协</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>地级政协,湖州市,市政协,浙江省</t>
+          <t>地级政协,嘉兴市,市政协,浙江省</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
@@ -13679,12 +13714,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>绍兴市政协</t>
+          <t>湖州市政协</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>地级政协,绍兴市,市政协,浙江省</t>
+          <t>地级政协,湖州市,市政协,浙江省</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -13714,12 +13749,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>金华市政协</t>
+          <t>绍兴市政协</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>地级政协,金华市,市政协,浙江省</t>
+          <t>地级政协,绍兴市,市政协,浙江省</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
@@ -13749,12 +13784,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>衢州市政协</t>
+          <t>金华市政协</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>地级政协,衢州市,市政协,浙江省</t>
+          <t>地级政协,金华市,市政协,浙江省</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
@@ -13784,12 +13819,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>舟山市政协</t>
+          <t>衢州市政协</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>地级政协,舟山市,市政协,浙江省</t>
+          <t>地级政协,衢州市,市政协,浙江省</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -13819,12 +13854,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>台州市政协</t>
+          <t>舟山市政协</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>地级政协,台州市,市政协,浙江省</t>
+          <t>地级政协,舟山市,市政协,浙江省</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
@@ -13854,12 +13889,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>丽水市政协</t>
+          <t>台州市政协</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>地级政协,丽水市,市政协,浙江省</t>
+          <t>地级政协,台州市,市政协,浙江省</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -13889,12 +13924,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>合肥市政协</t>
+          <t>丽水市政协</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>地级政协,合肥市,市政协,安徽省</t>
+          <t>地级政协,丽水市,市政协,浙江省</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
@@ -13924,12 +13959,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>芜湖市政协</t>
+          <t>合肥市政协</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>地级政协,芜湖市,市政协,安徽省</t>
+          <t>地级政协,合肥市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
@@ -13959,12 +13994,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>蚌埠市政协</t>
+          <t>芜湖市政协</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>地级政协,蚌埠市,市政协,安徽省</t>
+          <t>地级政协,芜湖市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF289" t="inlineStr">
@@ -13994,12 +14029,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>淮南市政协</t>
+          <t>蚌埠市政协</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>地级政协,淮南市,市政协,安徽省</t>
+          <t>地级政协,蚌埠市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -14029,12 +14064,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>马鞍山市政协</t>
+          <t>淮南市政协</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>地级政协,马鞍山市,市政协,安徽省</t>
+          <t>地级政协,淮南市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -14064,12 +14099,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>淮北市政协</t>
+          <t>马鞍山市政协</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>地级政协,淮北市,市政协,安徽省</t>
+          <t>地级政协,马鞍山市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -14099,12 +14134,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>铜陵市政协</t>
+          <t>淮北市政协</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>地级政协,铜陵市,市政协,安徽省</t>
+          <t>地级政协,淮北市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -14134,12 +14169,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>安庆市政协</t>
+          <t>铜陵市政协</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>地级政协,安庆市,市政协,安徽省</t>
+          <t>地级政协,铜陵市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -14169,12 +14204,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>黄山市政协</t>
+          <t>安庆市政协</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>地级政协,黄山市,市政协,安徽省</t>
+          <t>地级政协,安庆市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -14204,12 +14239,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>滁州市政协</t>
+          <t>黄山市政协</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>地级政协,滁州市,市政协,安徽省</t>
+          <t>地级政协,黄山市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -14239,12 +14274,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>阜阳市政协</t>
+          <t>滁州市政协</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>地级政协,阜阳市,市政协,安徽省</t>
+          <t>地级政协,滁州市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -14274,12 +14309,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>宿州市政协</t>
+          <t>阜阳市政协</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>地级政协,宿州市,市政协,安徽省</t>
+          <t>地级政协,阜阳市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF298" t="inlineStr">
@@ -14309,12 +14344,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>六安市政协</t>
+          <t>宿州市政协</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>地级政协,六安市,市政协,安徽省</t>
+          <t>地级政协,宿州市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
@@ -14344,12 +14379,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>亳州市政协</t>
+          <t>六安市政协</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>地级政协,亳州市,市政协,安徽省</t>
+          <t>地级政协,六安市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
@@ -14379,12 +14414,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>池州市政协</t>
+          <t>亳州市政协</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>地级政协,池州市,市政协,安徽省</t>
+          <t>地级政协,亳州市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF301" t="inlineStr">
@@ -14414,12 +14449,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>宣城市政协</t>
+          <t>池州市政协</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>地级政协,宣城市,市政协,安徽省</t>
+          <t>地级政协,池州市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
@@ -14449,12 +14484,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>福州市政协</t>
+          <t>宣城市政协</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>地级政协,福州市,市政协,福建省</t>
+          <t>地级政协,宣城市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
@@ -14484,12 +14519,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>莆田市政协</t>
+          <t>福州市政协</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>地级政协,莆田市,市政协,福建省</t>
+          <t>地级政协,福州市,市政协,福建省</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -14519,12 +14554,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>三明市政协</t>
+          <t>莆田市政协</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>地级政协,三明市,市政协,福建省</t>
+          <t>地级政协,莆田市,市政协,福建省</t>
         </is>
       </c>
       <c r="AF305" t="inlineStr">
@@ -14554,12 +14589,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>泉州市政协</t>
+          <t>三明市政协</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>地级政协,泉州市,市政协,福建省</t>
+          <t>地级政协,三明市,市政协,福建省</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
@@ -14589,12 +14624,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>漳州市政协</t>
+          <t>泉州市政协</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>地级政协,漳州市,市政协,福建省</t>
+          <t>地级政协,泉州市,市政协,福建省</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -14624,12 +14659,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>南平市政协</t>
+          <t>漳州市政协</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>地级政协,南平市,市政协,福建省</t>
+          <t>地级政协,漳州市,市政协,福建省</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
@@ -14659,12 +14694,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>龙岩市政协</t>
+          <t>南平市政协</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>地级政协,龙岩市,市政协,福建省</t>
+          <t>地级政协,南平市,市政协,福建省</t>
         </is>
       </c>
       <c r="AF309" t="inlineStr">
@@ -14694,12 +14729,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>宁德市政协</t>
+          <t>龙岩市政协</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>地级政协,宁德市,市政协,福建省</t>
+          <t>地级政协,龙岩市,市政协,福建省</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
@@ -14729,12 +14764,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>南昌市政协</t>
+          <t>宁德市政协</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>地级政协,南昌市,市政协,江西省</t>
+          <t>地级政协,宁德市,市政协,福建省</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
@@ -14764,12 +14799,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>景德镇市政协</t>
+          <t>南昌市政协</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>地级政协,景德镇市,市政协,江西省</t>
+          <t>地级政协,南昌市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -14799,12 +14834,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>萍乡市政协</t>
+          <t>景德镇市政协</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>地级政协,萍乡市,市政协,江西省</t>
+          <t>地级政协,景德镇市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
@@ -14834,12 +14869,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>九江市政协</t>
+          <t>萍乡市政协</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>地级政协,九江市,市政协,江西省</t>
+          <t>地级政协,萍乡市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -14869,12 +14904,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>新余市政协</t>
+          <t>九江市政协</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>地级政协,新余市,市政协,江西省</t>
+          <t>地级政协,九江市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
@@ -14904,12 +14939,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>鹰潭市政协</t>
+          <t>新余市政协</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>地级政协,鹰潭市,市政协,江西省</t>
+          <t>地级政协,新余市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -14939,12 +14974,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>赣州市政协</t>
+          <t>鹰潭市政协</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>地级政协,赣州市,市政协,江西省</t>
+          <t>地级政协,鹰潭市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
@@ -14974,12 +15009,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>吉安市政协</t>
+          <t>赣州市政协</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>地级政协,吉安市,市政协,江西省</t>
+          <t>地级政协,赣州市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -15009,12 +15044,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>宜春市政协</t>
+          <t>吉安市政协</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>地级政协,宜春市,市政协,江西省</t>
+          <t>地级政协,吉安市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -15044,12 +15079,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>抚州市政协</t>
+          <t>宜春市政协</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>地级政协,抚州市,市政协,江西省</t>
+          <t>地级政协,宜春市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -15079,12 +15114,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>上饶市政协</t>
+          <t>抚州市政协</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>地级政协,上饶市,市政协,江西省</t>
+          <t>地级政协,抚州市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
@@ -15114,12 +15149,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>淄博市政协</t>
+          <t>上饶市政协</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>地级政协,淄博市,市政协,山东省</t>
+          <t>地级政协,上饶市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
@@ -15149,12 +15184,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>枣庄市政协</t>
+          <t>淄博市政协</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>地级政协,枣庄市,市政协,山东省</t>
+          <t>地级政协,淄博市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
@@ -15184,12 +15219,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>东营市政协</t>
+          <t>枣庄市政协</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>地级政协,东营市,市政协,山东省</t>
+          <t>地级政协,枣庄市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
@@ -15219,12 +15254,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>烟台市政协</t>
+          <t>东营市政协</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>地级政协,烟台市,市政协,山东省</t>
+          <t>地级政协,东营市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -15254,12 +15289,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>潍坊市政协</t>
+          <t>烟台市政协</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>地级政协,潍坊市,市政协,山东省</t>
+          <t>地级政协,烟台市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
@@ -15289,12 +15324,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>济宁市政协</t>
+          <t>潍坊市政协</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>地级政协,济宁市,市政协,山东省</t>
+          <t>地级政协,潍坊市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF327" t="inlineStr">
@@ -15324,12 +15359,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>泰安市政协</t>
+          <t>济宁市政协</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>地级政协,泰安市,市政协,山东省</t>
+          <t>地级政协,济宁市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
@@ -15359,12 +15394,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>威海市政协</t>
+          <t>泰安市政协</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>地级政协,威海市,市政协,山东省</t>
+          <t>地级政协,泰安市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF329" t="inlineStr">
@@ -15394,12 +15429,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>日照市政协</t>
+          <t>威海市政协</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>地级政协,日照市,市政协,山东省</t>
+          <t>地级政协,威海市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -15429,12 +15464,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>临沂市政协</t>
+          <t>日照市政协</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>地级政协,临沂市,市政协,山东省</t>
+          <t>地级政协,日照市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -15464,12 +15499,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>德州市政协</t>
+          <t>临沂市政协</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>地级政协,德州市,市政协,山东省</t>
+          <t>地级政协,临沂市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
@@ -15499,12 +15534,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>聊城市政协</t>
+          <t>德州市政协</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>地级政协,聊城市,市政协,山东省</t>
+          <t>地级政协,德州市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
@@ -15534,12 +15569,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>滨州市政协</t>
+          <t>聊城市政协</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>地级政协,滨州市,市政协,山东省</t>
+          <t>地级政协,聊城市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF334" t="inlineStr">
@@ -15569,12 +15604,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>菏泽市政协</t>
+          <t>滨州市政协</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>地级政协,菏泽市,市政协,山东省</t>
+          <t>地级政协,滨州市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -15604,12 +15639,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>郑州市政协</t>
+          <t>菏泽市政协</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>地级政协,郑州市,市政协,河南省</t>
+          <t>地级政协,菏泽市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
@@ -15639,12 +15674,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>开封市政协</t>
+          <t>郑州市政协</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>地级政协,开封市,市政协,河南省</t>
+          <t>地级政协,郑州市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -15674,12 +15709,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>洛阳市政协</t>
+          <t>开封市政协</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>地级政协,洛阳市,市政协,河南省</t>
+          <t>地级政协,开封市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
@@ -15709,12 +15744,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>平顶山市政协</t>
+          <t>洛阳市政协</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>地级政协,平顶山市,市政协,河南省</t>
+          <t>地级政协,洛阳市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
@@ -15744,12 +15779,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>安阳市政协</t>
+          <t>平顶山市政协</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>地级政协,安阳市,市政协,河南省</t>
+          <t>地级政协,平顶山市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
@@ -15779,12 +15814,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>鹤壁市政协</t>
+          <t>安阳市政协</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>地级政协,鹤壁市,市政协,河南省</t>
+          <t>地级政协,安阳市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF341" t="inlineStr">
@@ -15814,12 +15849,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>新乡市政协</t>
+          <t>鹤壁市政协</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>地级政协,新乡市,市政协,河南省</t>
+          <t>地级政协,鹤壁市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF342" t="inlineStr">
@@ -15849,12 +15884,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>焦作市政协</t>
+          <t>新乡市政协</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>地级政协,焦作市,市政协,河南省</t>
+          <t>地级政协,新乡市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF343" t="inlineStr">
@@ -15884,12 +15919,12 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>濮阳市政协</t>
+          <t>焦作市政协</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>地级政协,濮阳市,市政协,河南省</t>
+          <t>地级政协,焦作市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -15919,12 +15954,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>许昌市政协</t>
+          <t>濮阳市政协</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>地级政协,许昌市,市政协,河南省</t>
+          <t>地级政协,濮阳市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF345" t="inlineStr">
@@ -15954,12 +15989,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>漯河市政协</t>
+          <t>许昌市政协</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>地级政协,漯河市,市政协,河南省</t>
+          <t>地级政协,许昌市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
@@ -15989,12 +16024,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>三门峡市政协</t>
+          <t>漯河市政协</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>地级政协,三门峡市,市政协,河南省</t>
+          <t>地级政协,漯河市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -16024,12 +16059,12 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>南阳市政协</t>
+          <t>三门峡市政协</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>地级政协,南阳市,市政协,河南省</t>
+          <t>地级政协,三门峡市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
@@ -16059,12 +16094,12 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>商丘市政协</t>
+          <t>南阳市政协</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>地级政协,商丘市,市政协,河南省</t>
+          <t>地级政协,南阳市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
@@ -16094,12 +16129,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>信阳市政协</t>
+          <t>商丘市政协</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>地级政协,信阳市,市政协,河南省</t>
+          <t>地级政协,商丘市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
@@ -16129,12 +16164,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>周口市政协</t>
+          <t>信阳市政协</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>地级政协,周口市,市政协,河南省</t>
+          <t>地级政协,信阳市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
@@ -16164,12 +16199,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>驻马店市政协</t>
+          <t>周口市政协</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>地级政协,驻马店市,市政协,河南省</t>
+          <t>地级政协,周口市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
@@ -16199,12 +16234,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>黄石市政协</t>
+          <t>驻马店市政协</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>地级政协,黄石市,市政协,湖北省</t>
+          <t>地级政协,驻马店市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -16234,12 +16269,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>十堰市政协</t>
+          <t>黄石市政协</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>地级政协,十堰市,市政协,湖北省</t>
+          <t>地级政协,黄石市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
@@ -16269,12 +16304,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>宜昌市政协</t>
+          <t>十堰市政协</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>地级政协,宜昌市,市政协,湖北省</t>
+          <t>地级政协,十堰市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
@@ -16304,12 +16339,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>襄阳市政协</t>
+          <t>宜昌市政协</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>地级政协,襄阳市,市政协,湖北省</t>
+          <t>地级政协,宜昌市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -16339,12 +16374,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>鄂州市政协</t>
+          <t>襄阳市政协</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>地级政协,鄂州市,市政协,湖北省</t>
+          <t>地级政协,襄阳市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
@@ -16374,12 +16409,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>荆门市政协</t>
+          <t>鄂州市政协</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>地级政协,荆门市,市政协,湖北省</t>
+          <t>地级政协,鄂州市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
@@ -16409,12 +16444,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>孝感市政协</t>
+          <t>荆门市政协</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>地级政协,孝感市,市政协,湖北省</t>
+          <t>地级政协,荆门市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF359" t="inlineStr">
@@ -16444,12 +16479,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>荆州市政协</t>
+          <t>孝感市政协</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>地级政协,荆州市,市政协,湖北省</t>
+          <t>地级政协,孝感市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF360" t="inlineStr">
@@ -16479,12 +16514,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>黄冈市政协</t>
+          <t>荆州市政协</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>地级政协,黄冈市,市政协,湖北省</t>
+          <t>地级政协,荆州市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF361" t="inlineStr">
@@ -16514,12 +16549,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>咸宁市政协</t>
+          <t>黄冈市政协</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>地级政协,咸宁市,市政协,湖北省</t>
+          <t>地级政协,黄冈市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -16549,12 +16584,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>随州市政协</t>
+          <t>咸宁市政协</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>地级政协,随州市,市政协,湖北省</t>
+          <t>地级政协,咸宁市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
@@ -16584,12 +16619,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>长沙市政协</t>
+          <t>随州市政协</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>地级政协,长沙市,市政协,湖南省</t>
+          <t>地级政协,随州市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
@@ -16619,12 +16654,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>株洲市政协</t>
+          <t>长沙市政协</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>地级政协,株洲市,市政协,湖南省</t>
+          <t>地级政协,长沙市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
@@ -16654,12 +16689,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>湘潭市政协</t>
+          <t>株洲市政协</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>地级政协,湘潭市,市政协,湖南省</t>
+          <t>地级政协,株洲市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
@@ -16689,12 +16724,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>衡阳市政协</t>
+          <t>湘潭市政协</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>地级政协,衡阳市,市政协,湖南省</t>
+          <t>地级政协,湘潭市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
@@ -16724,12 +16759,12 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>邵阳市政协</t>
+          <t>衡阳市政协</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>地级政协,邵阳市,市政协,湖南省</t>
+          <t>地级政协,衡阳市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">
@@ -16759,12 +16794,12 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>岳阳市政协</t>
+          <t>邵阳市政协</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>地级政协,岳阳市,市政协,湖南省</t>
+          <t>地级政协,邵阳市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
@@ -16794,12 +16829,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>常德市政协</t>
+          <t>岳阳市政协</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>地级政协,常德市,市政协,湖南省</t>
+          <t>地级政协,岳阳市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
@@ -16829,12 +16864,12 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>张家界市政协</t>
+          <t>常德市政协</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>地级政协,张家界市,市政协,湖南省</t>
+          <t>地级政协,常德市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF371" t="inlineStr">
@@ -16864,12 +16899,12 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>益阳市政协</t>
+          <t>张家界市政协</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>地级政协,益阳市,市政协,湖南省</t>
+          <t>地级政协,张家界市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
@@ -16899,12 +16934,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>郴州市政协</t>
+          <t>益阳市政协</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>地级政协,郴州市,市政协,湖南省</t>
+          <t>地级政协,益阳市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
@@ -16934,12 +16969,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>永州市政协</t>
+          <t>郴州市政协</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>地级政协,永州市,市政协,湖南省</t>
+          <t>地级政协,郴州市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
@@ -16969,12 +17004,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>怀化市政协</t>
+          <t>永州市政协</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>地级政协,怀化市,市政协,湖南省</t>
+          <t>地级政协,永州市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
@@ -17004,12 +17039,12 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>娄底市政协</t>
+          <t>怀化市政协</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>地级政协,娄底市,市政协,湖南省</t>
+          <t>地级政协,怀化市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
@@ -17039,12 +17074,12 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>南宁市政协</t>
+          <t>娄底市政协</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>地级政协,南宁市,市政协,广西壮族自治区</t>
+          <t>地级政协,娄底市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF377" t="inlineStr">
@@ -17074,12 +17109,12 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>柳州市政协</t>
+          <t>南宁市政协</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>地级政协,柳州市,市政协,广西壮族自治区</t>
+          <t>地级政协,南宁市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF378" t="inlineStr">
@@ -17109,12 +17144,12 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>桂林市政协</t>
+          <t>柳州市政协</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>地级政协,桂林市,市政协,广西壮族自治区</t>
+          <t>地级政协,柳州市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF379" t="inlineStr">
@@ -17144,12 +17179,12 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>梧州市政协</t>
+          <t>桂林市政协</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>地级政协,梧州市,市政协,广西壮族自治区</t>
+          <t>地级政协,桂林市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF380" t="inlineStr">
@@ -17179,12 +17214,12 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>北海市政协</t>
+          <t>梧州市政协</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>地级政协,北海市,市政协,广西壮族自治区</t>
+          <t>地级政协,梧州市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF381" t="inlineStr">
@@ -17214,12 +17249,12 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>防城港市政协</t>
+          <t>北海市政协</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>地级政协,防城港市,市政协,广西壮族自治区</t>
+          <t>地级政协,北海市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -17249,12 +17284,12 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>钦州市政协</t>
+          <t>防城港市政协</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>地级政协,钦州市,市政协,广西壮族自治区</t>
+          <t>地级政协,防城港市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF383" t="inlineStr">
@@ -17284,12 +17319,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>贵港市政协</t>
+          <t>钦州市政协</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>地级政协,贵港市,市政协,广西壮族自治区</t>
+          <t>地级政协,钦州市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -17319,12 +17354,12 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>玉林市政协</t>
+          <t>贵港市政协</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>地级政协,玉林市,市政协,广西壮族自治区</t>
+          <t>地级政协,贵港市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -17354,12 +17389,12 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>百色市政协</t>
+          <t>玉林市政协</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>地级政协,百色市,市政协,广西壮族自治区</t>
+          <t>地级政协,玉林市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF386" t="inlineStr">
@@ -17389,12 +17424,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>贺州市政协</t>
+          <t>百色市政协</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>地级政协,贺州市,市政协,广西壮族自治区</t>
+          <t>地级政协,百色市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF387" t="inlineStr">
@@ -17424,12 +17459,12 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>河池市政协</t>
+          <t>贺州市政协</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>地级政协,河池市,市政协,广西壮族自治区</t>
+          <t>地级政协,贺州市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF388" t="inlineStr">
@@ -17459,12 +17494,12 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>来宾市政协</t>
+          <t>河池市政协</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>地级政协,来宾市,市政协,广西壮族自治区</t>
+          <t>地级政协,河池市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF389" t="inlineStr">
@@ -17494,12 +17529,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>崇左市政协</t>
+          <t>来宾市政协</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>地级政协,崇左市,市政协,广西壮族自治区</t>
+          <t>地级政协,来宾市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -17529,12 +17564,12 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>海口市政协</t>
+          <t>崇左市政协</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>地级政协,海口市,市政协,海南省</t>
+          <t>地级政协,崇左市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF391" t="inlineStr">
@@ -17564,12 +17599,12 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>三亚市政协</t>
+          <t>海口市政协</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>地级政协,三亚市,市政协,海南省</t>
+          <t>地级政协,海口市,市政协,海南省</t>
         </is>
       </c>
       <c r="AF392" t="inlineStr">
@@ -17599,12 +17634,12 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>三沙市政协</t>
+          <t>三亚市政协</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>地级政协,三沙市,市政协,海南省</t>
+          <t>地级政协,三亚市,市政协,海南省</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -17634,12 +17669,12 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>儋州市政协</t>
+          <t>三沙市政协</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>地级政协,儋州市,市政协,海南省</t>
+          <t>地级政协,三沙市,市政协,海南省</t>
         </is>
       </c>
       <c r="AF394" t="inlineStr">
@@ -17669,12 +17704,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>自贡市政协</t>
+          <t>儋州市政协</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>地级政协,自贡市,市政协,四川省</t>
+          <t>地级政协,儋州市,市政协,海南省</t>
         </is>
       </c>
       <c r="AF395" t="inlineStr">
@@ -17704,12 +17739,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>攀枝花市政协</t>
+          <t>自贡市政协</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>地级政协,攀枝花市,市政协,四川省</t>
+          <t>地级政协,自贡市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -17739,12 +17774,12 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>泸州市政协</t>
+          <t>攀枝花市政协</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>地级政协,泸州市,市政协,四川省</t>
+          <t>地级政协,攀枝花市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF397" t="inlineStr">
@@ -17774,12 +17809,12 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>德阳市政协</t>
+          <t>泸州市政协</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>地级政协,德阳市,市政协,四川省</t>
+          <t>地级政协,泸州市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF398" t="inlineStr">
@@ -17809,12 +17844,12 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>绵阳市政协</t>
+          <t>德阳市政协</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>地级政协,绵阳市,市政协,四川省</t>
+          <t>地级政协,德阳市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF399" t="inlineStr">
@@ -17844,12 +17879,12 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>广元市政协</t>
+          <t>绵阳市政协</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>地级政协,广元市,市政协,四川省</t>
+          <t>地级政协,绵阳市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF400" t="inlineStr">
@@ -17879,12 +17914,12 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>遂宁市政协</t>
+          <t>广元市政协</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>地级政协,遂宁市,市政协,四川省</t>
+          <t>地级政协,广元市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF401" t="inlineStr">
@@ -17914,12 +17949,12 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>内江市政协</t>
+          <t>遂宁市政协</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>地级政协,内江市,市政协,四川省</t>
+          <t>地级政协,遂宁市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF402" t="inlineStr">
@@ -17949,12 +17984,12 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>乐山市政协</t>
+          <t>内江市政协</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>地级政协,乐山市,市政协,四川省</t>
+          <t>地级政协,内江市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF403" t="inlineStr">
@@ -17984,12 +18019,12 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>南充市政协</t>
+          <t>乐山市政协</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>地级政协,南充市,市政协,四川省</t>
+          <t>地级政协,乐山市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF404" t="inlineStr">
@@ -18019,12 +18054,12 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>眉山市政协</t>
+          <t>南充市政协</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>地级政协,眉山市,市政协,四川省</t>
+          <t>地级政协,南充市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF405" t="inlineStr">
@@ -18054,12 +18089,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>宜宾市政协</t>
+          <t>眉山市政协</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>地级政协,宜宾市,市政协,四川省</t>
+          <t>地级政协,眉山市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF406" t="inlineStr">
@@ -18089,12 +18124,12 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>广安市政协</t>
+          <t>宜宾市政协</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>地级政协,广安市,市政协,四川省</t>
+          <t>地级政协,宜宾市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF407" t="inlineStr">
@@ -18124,12 +18159,12 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>达州市政协</t>
+          <t>广安市政协</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>地级政协,达州市,市政协,四川省</t>
+          <t>地级政协,广安市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF408" t="inlineStr">
@@ -18159,12 +18194,12 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>雅安市政协</t>
+          <t>达州市政协</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>地级政协,雅安市,市政协,四川省</t>
+          <t>地级政协,达州市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF409" t="inlineStr">
@@ -18194,12 +18229,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>巴中市政协</t>
+          <t>雅安市政协</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>地级政协,巴中市,市政协,四川省</t>
+          <t>地级政协,雅安市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF410" t="inlineStr">
@@ -18229,12 +18264,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>资阳市政协</t>
+          <t>巴中市政协</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>地级政协,资阳市,市政协,四川省</t>
+          <t>地级政协,巴中市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF411" t="inlineStr">
@@ -18264,12 +18299,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>贵阳市政协</t>
+          <t>资阳市政协</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>地级政协,贵阳市,市政协,贵州省</t>
+          <t>地级政协,资阳市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF412" t="inlineStr">
@@ -18299,12 +18334,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>六盘水市政协</t>
+          <t>贵阳市政协</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>地级政协,六盘水市,市政协,贵州省</t>
+          <t>地级政协,贵阳市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -18334,12 +18369,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>遵义市政协</t>
+          <t>六盘水市政协</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>地级政协,遵义市,市政协,贵州省</t>
+          <t>地级政协,六盘水市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -18369,12 +18404,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>安顺市政协</t>
+          <t>遵义市政协</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>地级政协,安顺市,市政协,贵州省</t>
+          <t>地级政协,遵义市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF415" t="inlineStr">
@@ -18404,12 +18439,12 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>毕节市政协</t>
+          <t>安顺市政协</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>地级政协,毕节市,市政协,贵州省</t>
+          <t>地级政协,安顺市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF416" t="inlineStr">
@@ -18439,12 +18474,12 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>铜仁市政协</t>
+          <t>毕节市政协</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>地级政协,铜仁市,市政协,贵州省</t>
+          <t>地级政协,毕节市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF417" t="inlineStr">
@@ -18474,12 +18509,12 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>昆明市政协</t>
+          <t>铜仁市政协</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>地级政协,昆明市,市政协,贵州省</t>
+          <t>地级政协,铜仁市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF418" t="inlineStr">
@@ -18509,12 +18544,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>曲靖市政协</t>
+          <t>昆明市政协</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>地级政协,曲靖市,市政协,贵州省</t>
+          <t>地级政协,昆明市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF419" t="inlineStr">
@@ -18544,12 +18579,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>玉溪市政协</t>
+          <t>曲靖市政协</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>地级政协,玉溪市,市政协,贵州省</t>
+          <t>地级政协,曲靖市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF420" t="inlineStr">
@@ -18579,12 +18614,12 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>保山市政协</t>
+          <t>玉溪市政协</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>地级政协,保山市,市政协,贵州省</t>
+          <t>地级政协,玉溪市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF421" t="inlineStr">
@@ -18614,12 +18649,12 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>昭通市政协</t>
+          <t>保山市政协</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>地级政协,昭通市,市政协,贵州省</t>
+          <t>地级政协,保山市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF422" t="inlineStr">
@@ -18649,12 +18684,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>丽江市政协</t>
+          <t>昭通市政协</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>地级政协,丽江市,市政协,贵州省</t>
+          <t>地级政协,昭通市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF423" t="inlineStr">
@@ -18684,12 +18719,12 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>普洱市政协</t>
+          <t>丽江市政协</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>地级政协,普洱市,市政协,贵州省</t>
+          <t>地级政协,丽江市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF424" t="inlineStr">
@@ -18719,12 +18754,12 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>临沧市政协</t>
+          <t>普洱市政协</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>地级政协,临沧市,市政协,贵州省</t>
+          <t>地级政协,普洱市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF425" t="inlineStr">
@@ -18754,12 +18789,12 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>拉萨市政协</t>
+          <t>临沧市政协</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>地级政协,拉萨市,市政协,贵州省</t>
+          <t>地级政协,临沧市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF426" t="inlineStr">
@@ -18789,12 +18824,12 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>日喀则市政协</t>
+          <t>拉萨市政协</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>地级政协,日喀则市,市政协,贵州省</t>
+          <t>地级政协,拉萨市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF427" t="inlineStr">
@@ -18824,12 +18859,12 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>昌都市政协</t>
+          <t>日喀则市政协</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>地级政协,昌都市,市政协,贵州省</t>
+          <t>地级政协,日喀则市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF428" t="inlineStr">
@@ -18859,12 +18894,12 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>林芝市政协</t>
+          <t>昌都市政协</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>地级政协,林芝市,市政协,贵州省</t>
+          <t>地级政协,昌都市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF429" t="inlineStr">
@@ -18894,12 +18929,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>山南市政协</t>
+          <t>林芝市政协</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>地级政协,山南市,市政协,贵州省</t>
+          <t>地级政协,林芝市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF430" t="inlineStr">
@@ -18929,12 +18964,12 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>那曲市政协</t>
+          <t>山南市政协</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>地级政协,那曲市,市政协,贵州省</t>
+          <t>地级政协,山南市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF431" t="inlineStr">
@@ -18964,12 +18999,12 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>铜川市政协</t>
+          <t>那曲市政协</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>地级政协,铜川市,市政协,陕西省</t>
+          <t>地级政协,那曲市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF432" t="inlineStr">
@@ -18999,12 +19034,12 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>宝鸡市政协</t>
+          <t>铜川市政协</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>地级政协,宝鸡市,市政协,陕西省</t>
+          <t>地级政协,铜川市,市政协,陕西省</t>
         </is>
       </c>
       <c r="AF433" t="inlineStr">
@@ -19034,12 +19069,12 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>咸阳市政协</t>
+          <t>宝鸡市政协</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>地级政协,咸阳市,市政协,陕西省</t>
+          <t>地级政协,宝鸡市,市政协,陕西省</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr">
@@ -19069,12 +19104,12 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>渭南市政协</t>
+          <t>咸阳市政协</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>地级政协,渭南市,市政协,陕西省</t>
+          <t>地级政协,咸阳市,市政协,陕西省</t>
         </is>
       </c>
       <c r="AF435" t="inlineStr">
@@ -19104,12 +19139,12 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>延安市政协</t>
+          <t>渭南市政协</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>地级政协,延安市,市政协,陕西省</t>
+          <t>地级政协,渭南市,市政协,陕西省</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
@@ -19139,12 +19174,12 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>汉中市政协</t>
+          <t>延安市政协</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>地级政协,汉中市,市政协,陕西省</t>
+          <t>地级政协,延安市,市政协,陕西省</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
@@ -19174,12 +19209,12 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>榆林市政协</t>
+          <t>汉中市政协</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>地级政协,榆林市,市政协,陕西省</t>
+          <t>地级政协,汉中市,市政协,陕西省</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
@@ -19209,12 +19244,12 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>安康市政协</t>
+          <t>榆林市政协</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>地级政协,安康市,市政协,陕西省</t>
+          <t>地级政协,榆林市,市政协,陕西省</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
@@ -19244,12 +19279,12 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>商洛市政协</t>
+          <t>安康市政协</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>地级政协,商洛市,市政协,陕西省</t>
+          <t>地级政协,安康市,市政协,陕西省</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
@@ -19279,12 +19314,12 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>兰州市政协</t>
+          <t>商洛市政协</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>地级政协,兰州市,市政协,甘肃省</t>
+          <t>地级政协,商洛市,市政协,陕西省</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
@@ -19314,12 +19349,12 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>嘉峪关市政协</t>
+          <t>兰州市政协</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>地级政协,嘉峪关市,市政协,甘肃省</t>
+          <t>地级政协,兰州市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF442" t="inlineStr">
@@ -19349,12 +19384,12 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>金昌市政协</t>
+          <t>嘉峪关市政协</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>地级政协,金昌市,市政协,甘肃省</t>
+          <t>地级政协,嘉峪关市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF443" t="inlineStr">
@@ -19384,12 +19419,12 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>白银市政协</t>
+          <t>金昌市政协</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>地级政协,白银市,市政协,甘肃省</t>
+          <t>地级政协,金昌市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -19419,12 +19454,12 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>天水市政协</t>
+          <t>白银市政协</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>地级政协,天水市,市政协,甘肃省</t>
+          <t>地级政协,白银市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
@@ -19454,12 +19489,12 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>武威市政协</t>
+          <t>天水市政协</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>地级政协,武威市,市政协,甘肃省</t>
+          <t>地级政协,天水市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
@@ -19489,12 +19524,12 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>张掖市政协</t>
+          <t>武威市政协</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>地级政协,张掖市,市政协,甘肃省</t>
+          <t>地级政协,武威市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
@@ -19524,12 +19559,12 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>平凉市政协</t>
+          <t>张掖市政协</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>地级政协,平凉市,市政协,甘肃省</t>
+          <t>地级政协,张掖市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
@@ -19559,12 +19594,12 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>酒泉市政协</t>
+          <t>平凉市政协</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>地级政协,酒泉市,市政协,甘肃省</t>
+          <t>地级政协,平凉市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
@@ -19594,12 +19629,12 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>庆阳市政协</t>
+          <t>酒泉市政协</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>地级政协,庆阳市,市政协,甘肃省</t>
+          <t>地级政协,酒泉市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF450" t="inlineStr">
@@ -19629,12 +19664,12 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>定西市政协</t>
+          <t>庆阳市政协</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>地级政协,定西市,市政协,甘肃省</t>
+          <t>地级政协,庆阳市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
@@ -19664,12 +19699,12 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>陇南市政协</t>
+          <t>定西市政协</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>地级政协,陇南市,市政协,甘肃省</t>
+          <t>地级政协,定西市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
@@ -19699,12 +19734,12 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>西宁市政协</t>
+          <t>陇南市政协</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>地级政协,西宁市,市政协,青海省</t>
+          <t>地级政协,陇南市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
@@ -19734,12 +19769,12 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>海东市政协</t>
+          <t>西宁市政协</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>地级政协,海东市,市政协,青海省</t>
+          <t>地级政协,西宁市,市政协,青海省</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
@@ -19769,12 +19804,12 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>银川市政协</t>
+          <t>海东市政协</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>地级政协,银川市,市政协,宁夏回族自治区</t>
+          <t>地级政协,海东市,市政协,青海省</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
@@ -19804,12 +19839,12 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>石嘴山市政协</t>
+          <t>银川市政协</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>地级政协,石嘴山市,市政协,宁夏回族自治区</t>
+          <t>地级政协,银川市,市政协,宁夏回族自治区</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
@@ -19839,12 +19874,12 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>吴忠市政协</t>
+          <t>石嘴山市政协</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>地级政协,吴忠市,市政协,宁夏回族自治区</t>
+          <t>地级政协,石嘴山市,市政协,宁夏回族自治区</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
@@ -19874,12 +19909,12 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>固原市政协</t>
+          <t>吴忠市政协</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>地级政协,固原市,市政协,宁夏回族自治区</t>
+          <t>地级政协,吴忠市,市政协,宁夏回族自治区</t>
         </is>
       </c>
       <c r="AF458" t="inlineStr">
@@ -19909,12 +19944,12 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>中卫市政协</t>
+          <t>固原市政协</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>地级政协,中卫市,市政协,宁夏回族自治区</t>
+          <t>地级政协,固原市,市政协,宁夏回族自治区</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
@@ -19944,12 +19979,12 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>乌鲁木齐市政协</t>
+          <t>中卫市政协</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>地级政协,乌鲁木齐市,市政协,新疆维吾尔自治区</t>
+          <t>地级政协,中卫市,市政协,宁夏回族自治区</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
@@ -19979,12 +20014,12 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>克拉玛依市政协</t>
+          <t>乌鲁木齐市政协</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>地级政协,克拉玛依市,市政协,新疆维吾尔自治区</t>
+          <t>地级政协,乌鲁木齐市,市政协,新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
@@ -20014,12 +20049,12 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>吐鲁番市政协</t>
+          <t>克拉玛依市政协</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>地级政协,吐鲁番市,市政协,新疆维吾尔自治区</t>
+          <t>地级政协,克拉玛依市,市政协,新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
@@ -20049,15 +20084,50 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
+          <t>吐鲁番市政协</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>地级政协,吐鲁番市,市政协,新疆维吾尔自治区</t>
+        </is>
+      </c>
+      <c r="AF463" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>政协</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>1</v>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
           <t>哈密市政协</t>
         </is>
       </c>
-      <c r="I463" t="inlineStr">
+      <c r="I464" t="inlineStr">
         <is>
           <t>地级政协,哈密市,市政协,新疆维吾尔自治区</t>
         </is>
       </c>
-      <c r="AF463" t="inlineStr">
+      <c r="AF464" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/assets/xlsx/cards.unified.xlsx
+++ b/assets/xlsx/cards.unified.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF464"/>
+  <dimension ref="A1:AG464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,21 +577,26 @@
           <t>enabled</t>
         </is>
       </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>is_ad</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>综合搜索</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -599,27 +604,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Google 搜索</t>
+          <t>全国人民代表大会</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>谷歌搜索引擎，全球索引量最大的多语综合搜索，学术、地图、翻译等延伸服务齐全</t>
+          <t>最高国家权力机关，行使国家立法权，官方网站发布法律、公报与常委会信息。</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>搜索引擎,聚合搜索</t>
+          <t>人大,全国人大,国家立法</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>访问官网 - www.google.com</t>
+          <t>访问官网 - www.npc.gov.cn</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://www.google.com</t>
+          <t>https://www.npc.gov.cn</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -631,17 +636,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>综合搜索</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -649,27 +654,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>必应 Bing</t>
+          <t>北京市人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>微软旗下综合搜索，深度集成 Windows 与 Copilot AI 智能应答</t>
+          <t>北京市人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>搜索引擎,聚合搜索</t>
+          <t>人大,北京,直辖市</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>访问官网 - www.bing.com</t>
+          <t>访问官网 - www.bjrd.gov.cn</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.bing.com</t>
+          <t>https://www.bjrd.gov.cn</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -681,17 +686,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>综合搜索</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -699,27 +704,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>上海市人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>中文网页与语义理解见长，贴吧、知道、百科构成内容生态闭环</t>
+          <t>上海市人民代表大会常设机关，地方立法与监督工作平台。</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>搜索引擎,聚合搜索</t>
+          <t>人大,上海,直辖市</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>访问官网 - www.baidu.com</t>
+          <t>访问官网 - www.shrd.gov.cn</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.baidu.com</t>
+          <t>https://www.shrd.gov.cn</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -731,17 +736,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>购物</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -749,27 +754,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>淘宝</t>
+          <t>天津市人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>电商商品与店铺检索，支持销量、价格、信用筛选与直播带货</t>
+          <t>天津市人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>搜索引擎,聚合搜索</t>
+          <t>人大,天津,直辖市</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>访问官网 - www.taobao.com</t>
+          <t>访问官网 - www.tjrd.gov.cn</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.taobao.com</t>
+          <t>https://www.tjrd.gov.cn</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -781,17 +786,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>购物</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -799,27 +804,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>京东</t>
+          <t>重庆市人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>自营与品牌电商检索，以物流时效与正品保障为特色的购物搜索</t>
+          <t>重庆市人民代表大会常设机关，地方立法与代表工作平台。</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>搜索引擎,聚合搜索</t>
+          <t>人大,重庆,直辖市</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>访问官网 - www.jd.com</t>
+          <t>访问官网 - www.cqrd.gov.cn</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.jd.com</t>
+          <t>https://www.cqrd.gov.cn</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -831,17 +836,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>购物</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -849,27 +854,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>拼多多</t>
+          <t>河北省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>低价拼团模式下的商品搜索，下沉市场供给与农货丰富</t>
+          <t>河北省人民代表大会常设机关，发布地方立法、监督与代表履职信息。</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>搜索引擎,聚合搜索</t>
+          <t>人大,河北,省</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>访问官网 - mobile.yangkeduo.com</t>
+          <t>访问官网 - www.hbrd.gov.cn</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com</t>
+          <t>https://www.hbrd.gov.cn</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -881,17 +886,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>社区知识</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -899,27 +904,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>知乎</t>
+          <t>山西省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>高质量中文问答社区，专业答主长文与观点检索入口</t>
+          <t>山西省人民代表大会常设机关，发布地方性法规与监督工作信息。</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>搜索引擎,聚合搜索</t>
+          <t>人大,山西,省</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>访问官网 - www.zhihu.com</t>
+          <t>访问官网 - www.sxpc.gov.cn</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.zhihu.com</t>
+          <t>https://www.sxpc.gov.cn</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -931,17 +936,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>社区知识</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -949,27 +954,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>维基百科</t>
+          <t>辽宁省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>非营利的协作百科，引用可追溯、跨语言词条互链</t>
+          <t>辽宁省人民代表大会常设机关，发布地方立法与代表工作信息。</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>搜索引擎,聚合搜索</t>
+          <t>人大,辽宁,省</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>访问官网 - zh.wikipedia.org</t>
+          <t>访问官网 - www.lnrd.gov.cn</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://zh.wikipedia.org</t>
+          <t>https://www.lnrd.gov.cn</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -981,17 +986,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>社区知识</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -999,27 +1004,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>微信搜一搜</t>
+          <t>吉林省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>检索公众号文章、视频号与朋友圈内容，封闭生态内搜索</t>
+          <t>吉林省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>搜索引擎,聚合搜索</t>
+          <t>人大,吉林,省</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>访问官网 - weixin.sogou.com</t>
+          <t>访问官网 - www.jlrd.gov.cn</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://weixin.sogou.com</t>
+          <t>https://www.jlrd.gov.cn</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1031,17 +1036,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>社区知识</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1049,27 +1054,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>头条搜索</t>
+          <t>黑龙江省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>基于字节推荐算法的通用搜索，信息流与热点聚合</t>
+          <t>黑龙江省人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>搜索引擎,聚合搜索</t>
+          <t>人大,黑龙江,省</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>访问官网 - so.toutiao.com</t>
+          <t>访问官网 - www.hljrd.gov.cn</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://so.toutiao.com</t>
+          <t>https://www.hljrd.gov.cn</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1081,17 +1086,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>视频</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1099,27 +1104,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>哔哩哔哩</t>
+          <t>江苏省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ACG 与 UP 主视频检索，弹幕文化与番剧社区入口</t>
+          <t>江苏省人民代表大会常设机关，地方立法与监督工作平台。</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>搜索引擎,聚合搜索</t>
+          <t>人大,江苏,省</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>访问官网 - www.bilibili.com</t>
+          <t>访问官网 - www.jsrd.gov.cn</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.bilibili.com</t>
+          <t>https://www.jsrd.gov.cn</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1131,17 +1136,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>视频</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1149,27 +1154,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>抖音</t>
+          <t>浙江省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>短视频内容搜索，按热点与挑战标签分发与发现</t>
+          <t>浙江省人民代表大会常设机关，发布地方性法规与代表信息。</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>搜索引擎,聚合搜索</t>
+          <t>人大,浙江,省</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>访问官网 - www.douyin.com</t>
+          <t>访问官网 - www.zjrd.gov.cn</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.douyin.com</t>
+          <t>https://www.zjrd.gov.cn</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -1181,17 +1186,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>开发</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1199,27 +1204,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>安徽省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>代码仓库与开源项目检索，支持 Issue、PR 与代码全文搜索</t>
+          <t>安徽省人民代表大会常设机关，发布地方立法与代表履职信息。</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>搜索引擎,聚合搜索</t>
+          <t>人大,安徽,省</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>访问官网 - github.com</t>
+          <t>访问官网 - www.ahrd.gov.cn</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://github.com</t>
+          <t>https://www.ahrd.gov.cn</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -1231,17 +1236,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>开发</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1249,27 +1254,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stack Overflow</t>
+          <t>福建省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>编程报错与技术方案问答检索，按投票质量排序</t>
+          <t>福建省人民代表大会常设机关，发布地方性法规与监督工作信息。</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>搜索引擎,聚合搜索</t>
+          <t>人大,福建,省</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>访问官网 - stackoverflow.com</t>
+          <t>访问官网 - www.fjrd.gov.cn</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://stackoverflow.com</t>
+          <t>https://www.fjrd.gov.cn</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -1281,17 +1286,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>开发</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1299,27 +1304,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>掘金</t>
+          <t>江西省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>前端、客户端与后端技术文章、教程与专栏检索</t>
+          <t>江西省人民代表大会常设机关，发布地方立法与代表工作信息。</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>搜索引擎,聚合搜索</t>
+          <t>人大,江西,省</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>访问官网 - juejin.cn</t>
+          <t>访问官网 - www.jxrd.gov.cn</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://juejin.cn</t>
+          <t>https://www.jxrd.gov.cn</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -1331,17 +1336,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1349,27 +1354,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>高德地图</t>
+          <t>山东省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>POI 地点、路线与实时路况检索，含打车与周边服务</t>
+          <t>山东省人民代表大会常设机关，地方立法与监督工作平台。</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>搜索引擎,聚合搜索</t>
+          <t>人大,山东,省</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>访问官网 - www.amap.com</t>
+          <t>访问官网 - www.sdrd.gov.cn</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.amap.com</t>
+          <t>https://www.sdrd.gov.cn</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -1381,17 +1386,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1399,27 +1404,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>有道翻译</t>
+          <t>河南省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>中英及多语词典与整句翻译，支持文档与网页翻译</t>
+          <t>河南省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>搜索引擎,聚合搜索</t>
+          <t>人大,河南,省</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>访问官网 - www.youdao.com</t>
+          <t>访问官网 - www.henanrd.gov.cn</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.youdao.com</t>
+          <t>https://www.henanrd.gov.cn</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -1431,17 +1436,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1449,27 +1454,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>网易云音乐</t>
+          <t>湖北省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>歌曲、歌单与歌词检索推荐，以乐评社区为特色</t>
+          <t>湖北省人民代表大会常设机关，地方立法与代表工作平台。</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>搜索引擎,聚合搜索</t>
+          <t>人大,湖北,省</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>访问官网 - music.163.com</t>
+          <t>访问官网 - www.hppc.gov.cn</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://music.163.com</t>
+          <t>https://www.hppc.gov.cn</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -1481,17 +1486,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>数据库</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1499,22 +1504,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>在线读报</t>
+          <t>湖南省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>九星时代报刊在线系统包含了综合报、晨报、日报、晚报、都市报、经济报、生活报、法制报、农业报、军事报、体育报、青少年、保健报和其他14大类的报纸资源，可以充分的满足不同用户的阅读需求。 使用指南 缩放功能 单击报纸任何一点，便可将报纸整版放大，同理单击放大后的报纸任意一处，即可缩小。同时也可用右侧操作项进行放大缩小。拖动功能 ：当报纸放大后，手指可随意拖动整版报纸，将超出显示区位置的报纸托动至显示区内。翻页功能：点住报纸画面，向左或向右横向滑动，即可将报纸翻页。</t>
+          <t>湖南省人民代表大会常设机关，发布地方性法规与监督信息。</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>人大,湖南,省</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>访问首页 - 202.106.125.196</t>
+          <t>访问官网 - www.hnrd.gov.cn</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>http://202.106.125.196</t>
+          <t>https://www.hnrd.gov.cn</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -1526,17 +1536,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>数据库</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1544,17 +1554,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>国务院政策文件库</t>
+          <t>广东省人民代表大会常务委员会</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>广东省人民代表大会常设机关，发布地方性法规与监督信息。</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>人大,广东,省</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>访问官网 - sousuo.www.gov.cn/zcwjk/</t>
+          <t>访问官网 - www.rd.gd.cn</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://sousuo.www.gov.cn/zcwjk/</t>
+          <t>https://www.rd.gd.cn</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -1566,17 +1586,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>综合搜索</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1584,27 +1604,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DuckDuckGo</t>
+          <t>海南省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>隐私搜索引擎，不收集用户信息、无广告</t>
+          <t>海南省人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>搜索引擎,隐私</t>
+          <t>人大,海南,省</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>访问官网 - duckduckgo.com</t>
+          <t>访问官网 - www.hainanpc.gov.cn</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://duckduckgo.com/</t>
+          <t>https://www.hainanpc.gov.cn</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -1616,17 +1636,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>综合搜索</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1634,27 +1654,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yandex</t>
+          <t>四川省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>俄罗斯主流综合搜索引擎</t>
+          <t>四川省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>搜索引擎</t>
+          <t>人大,四川,省</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>访问官网 - yandex.com</t>
+          <t>访问官网 - www.scspc.gov.cn</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://yandex.com/</t>
+          <t>https://www.scspc.gov.cn</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -1666,17 +1686,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>综合搜索</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1684,27 +1704,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qwant</t>
+          <t>贵州省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>法国搜索引擎，注重隐私保护</t>
+          <t>贵州省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>搜索引擎,隐私</t>
+          <t>人大,贵州,省</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>访问官网 - www.qwant.com</t>
+          <t>访问官网 - www.gzrd.gov.cn</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.qwant.com/</t>
+          <t>https://www.gzrd.gov.cn</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -1716,17 +1736,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>综合搜索</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1734,27 +1754,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Perplexity</t>
+          <t>云南省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>对话式 AI 搜索引擎，直接给出带引用的答案</t>
+          <t>云南省人民代表大会常设机关，发布地方立法与代表履职信息。</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>搜索引擎,AI搜索</t>
+          <t>人大,云南,省</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>访问官网 - www.perplexity.ai</t>
+          <t>访问官网 - www.ynrd.gov.cn</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.perplexity.ai/</t>
+          <t>https://www.ynrd.gov.cn</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -1766,17 +1786,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>综合搜索</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1784,27 +1804,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>You.com</t>
+          <t>陕西省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AI 搜索引擎，整合多模型结果并支持对话</t>
+          <t>陕西省人民代表大会常设机关，发布地方性法规与监督工作信息。</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>搜索引擎,AI搜索</t>
+          <t>人大,陕西,省</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>访问官网 - you.com</t>
+          <t>访问官网 - www.sxrd.gov.cn</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://you.com/</t>
+          <t>https://www.sxrd.gov.cn</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -1816,17 +1836,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>综合搜索</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1834,27 +1854,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Felo</t>
+          <t>甘肃省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>免费 AI 智能搜索引擎，支持多语问答</t>
+          <t>甘肃省人民代表大会常设机关，发布地方立法与代表工作信息。</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>搜索引擎,AI搜索</t>
+          <t>人大,甘肃,省</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>访问官网 - felo.ai</t>
+          <t>访问官网 - www.gsrdw.gov.cn</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://felo.ai/search</t>
+          <t>https://www.gsrdw.gov.cn</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -1866,17 +1886,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>社区知识</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1884,27 +1904,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>知乎搜索</t>
+          <t>青海省人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>搜索知乎站内的问答与文章</t>
+          <t>青海省人民代表大会常设机关，发布地方性法规与监督信息。</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>搜索引擎,社区</t>
+          <t>人大,青海,省</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>访问官网 - zhihu.sogou.com</t>
+          <t>访问官网 - www.qhrd.gov.cn</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://zhihu.sogou.com/</t>
+          <t>https://www.qhrd.gov.cn</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -1916,17 +1936,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>社区知识</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1934,27 +1954,27 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WikiHow</t>
+          <t>内蒙古自治区人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>综合技能与万事指南搜索站</t>
+          <t>内蒙古自治区人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>知识,指南</t>
+          <t>人大,内蒙古,自治区</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>访问官网 - zh.wikihow.com</t>
+          <t>访问官网 - www.nmgrd.gov.cn</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://zh.wikihow.com/</t>
+          <t>https://www.nmgrd.gov.cn</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -1966,17 +1986,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>开发</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1984,27 +2004,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>开发者搜索</t>
+          <t>广西壮族自治区人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>百度面向开发者的垂直搜索引擎</t>
+          <t>广西壮族自治区人民代表大会常设机关，发布地方立法与代表履职信息。</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>搜索引擎,开发</t>
+          <t>人大,广西,自治区</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>访问官网 - kaifa.baidu.com</t>
+          <t>访问官网 - www.gxrd.gov.cn</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://kaifa.baidu.com/</t>
+          <t>https://www.gxrd.gov.cn</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -2016,17 +2036,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2034,27 +2054,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TinEye</t>
+          <t>西藏自治区人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>以图搜图的反向图片检索搜索引擎</t>
+          <t>西藏自治区人民代表大会常设机关，发布地方立法与监督信息。</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>以图搜图,工具</t>
+          <t>人大,西藏,自治区</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>访问官网 - www.tineye.com</t>
+          <t>访问官网 - www.xizangrd.gov.cn</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.tineye.com</t>
+          <t>https://www.xizangrd.gov.cn</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -2066,17 +2086,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2084,27 +2104,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>网站历史快照</t>
+          <t>宁夏回族自治区人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Internet Archive 查看网站历史存档快照</t>
+          <t>宁夏回族自治区人民代表大会常设机关，发布地方性法规与代表工作信息。</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>工具,归档</t>
+          <t>人大,宁夏,自治区</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>访问官网 - archive.org</t>
+          <t>访问官网 - www.nxrd.gov.cn</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://archive.org/</t>
+          <t>https://www.nxrd.gov.cn</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -2116,17 +2136,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2134,27 +2154,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>新疆维吾尔自治区人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>查看并分析任意网站的流量与排名</t>
+          <t>新疆维吾尔自治区人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>工具,分析</t>
+          <t>人大,新疆,自治区</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>访问官网 - www.similarweb.com</t>
+          <t>访问官网 - www.xjpcsc.gov.cn</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.similarweb.com/zh/</t>
+          <t>https://www.xjpcsc.gov.cn</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -2166,17 +2186,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>国务院</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -2184,27 +2204,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>相似网站</t>
+          <t>中华人民共和国中央人民政府（国务院）</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>寻找功能相似的网站推荐</t>
+          <t>国务院官方网站，国家政务总门户，发布政策法规与政务信息。</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>工具,发现</t>
+          <t>政务,国务院,中央政府</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>访问官网 - www.similarsitesearch.com</t>
+          <t>访问官网 - www.gov.cn</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.similarsitesearch.com/</t>
+          <t>https://www.gov.cn</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -2216,17 +2236,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>国家平台</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -2234,27 +2254,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Windy</t>
+          <t>国家政务服务平台</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>可视化天气数据与气象预报查询</t>
+          <t>全国统一政务服务平台，提供在线办事、政务服务与效能监督。</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>工具,天气</t>
+          <t>政务,服务平台,在线办事</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>访问官网 - www.windy.com</t>
+          <t>访问官网 - gjzwfw.www.gov.cn</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.windy.com/</t>
+          <t>https://gjzwfw.www.gov.cn</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -2266,17 +2286,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -2284,27 +2304,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Google 图书</t>
+          <t>外交部</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>检索正规出版书籍、杂志、报纸的摘要</t>
+          <t>主管外交事务，发布外交政策、双边关系与国际交往信息。</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>图书,搜索</t>
+          <t>政务,外交,外交部</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>访问官网 - books.google.com</t>
+          <t>访问官网 - www.mfa.gov.cn</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://books.google.com/</t>
+          <t>https://www.mfa.gov.cn</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -2316,17 +2336,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>素材</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -2334,27 +2354,27 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CC Search</t>
+          <t>国防部</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>检索可免费使用的无版权图片资源</t>
+          <t>中华人民共和国国防部，发布国防政策、军队建设与权威军事信息。</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>图片,素材</t>
+          <t>政务,国防,国防部</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>访问官网 - ccsearch.creativecommons.org</t>
+          <t>访问官网 - www.mod.gov.cn</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://ccsearch.creativecommons.org/</t>
+          <t>https://www.mod.gov.cn</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -2366,17 +2386,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>素材</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -2384,27 +2404,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pexels</t>
+          <t>国家发展和改革委员会</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>高质量免费图片与视频素材库</t>
+          <t>宏观经济综合管理，拟订发展战略与规划。</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>图片,素材</t>
+          <t>政务,发改委,宏观经济</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>访问官网 - www.pexels.com</t>
+          <t>访问官网 - www.ndrc.gov.cn</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.pexels.com/</t>
+          <t>https://www.ndrc.gov.cn</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -2416,17 +2436,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>素材</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -2434,27 +2454,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Unsplash</t>
+          <t>教育部</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>免费高清图片素材社区</t>
+          <t>主管教育事业与语言文字工作，发布教育政策。</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>图片,素材</t>
+          <t>政务,教育,教育部</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>访问官网 - unsplash.com</t>
+          <t>访问官网 - www.moe.gov.cn</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://unsplash.com/</t>
+          <t>https://www.moe.gov.cn</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -2466,17 +2486,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>素材</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -2484,27 +2504,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LibreStock</t>
+          <t>科学技术部</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>检索多家图库的优质高清图片</t>
+          <t>主管科技发展与创新，发布科技政策与研发计划信息。</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>图片,素材</t>
+          <t>政务,科技,科技部</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>访问官网 - librestock.com</t>
+          <t>访问官网 - www.most.gov.cn</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://librestock.com/</t>
+          <t>https://www.most.gov.cn</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -2516,17 +2536,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>素材</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2534,27 +2554,27 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Iconfinder</t>
+          <t>工业和信息化部</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>查找 logo 等矢量图标素材</t>
+          <t>主管工业与信息化产业发展与行业管理。</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>图标,素材</t>
+          <t>政务,工信,信息化</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>访问官网 - www.iconfinder.com</t>
+          <t>访问官网 - www.miit.gov.cn</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.iconfinder.com/</t>
+          <t>https://www.miit.gov.cn</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -2566,17 +2586,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>素材</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2584,27 +2604,27 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FindIcons</t>
+          <t>国家民族事务委员会</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>优秀图标素材库检索</t>
+          <t>主管民族事务与民族团结进步工作，发布民族政策信息。</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>图标,素材</t>
+          <t>政务,民委,民族事务</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>访问官网 - findicons.com</t>
+          <t>访问官网 - www.neac.gov.cn</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://findicons.com/</t>
+          <t>https://www.neac.gov.cn</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -2616,17 +2636,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>学术搜索</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2634,27 +2654,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>谷歌学术</t>
+          <t>公安部</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Google 提供的免费学术文章搜索</t>
+          <t>维护社会治安，主管公安工作。</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>学术,搜索</t>
+          <t>政务,公安,公安部</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>访问官网 - scholar.google.com</t>
+          <t>访问官网 - www.mps.gov.cn</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/</t>
+          <t>https://www.mps.gov.cn</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -2666,17 +2686,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>学术搜索</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2684,27 +2704,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>百度学术</t>
+          <t>民政部</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>百度学术信息搜索引擎</t>
+          <t>主管民政事务、社会救助与社会组织管理。</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>学术,搜索</t>
+          <t>政务,民政,民政部</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>访问官网 - xueshu.baidu.com</t>
+          <t>访问官网 - www.mca.gov.cn</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://xueshu.baidu.com/</t>
+          <t>https://www.mca.gov.cn</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -2716,17 +2736,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>学术搜索</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -2734,27 +2754,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>中国知网</t>
+          <t>司法部</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>精品论文与学术资源检索平台</t>
+          <t>主管司法行政、法治建设与法律服务。</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>学术,数据库</t>
+          <t>政务,司法,司法部</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>访问官网 - www.cnki.net</t>
+          <t>访问官网 - www.moj.gov.cn</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.cnki.net/</t>
+          <t>https://www.moj.gov.cn</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -2766,17 +2786,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>学术搜索</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2784,27 +2804,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Semantic Scholar</t>
+          <t>财政部</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>免费学术搜索引擎（期刊/会议资料）</t>
+          <t>主管国家财政收支与财税政策。</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>学术,搜索</t>
+          <t>政务,财政,财政部</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>访问官网 - www.semanticscholar.org</t>
+          <t>访问官网 - www.mof.gov.cn</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.semanticscholar.org/</t>
+          <t>https://www.mof.gov.cn</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -2816,17 +2836,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>学术搜索</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -2834,27 +2854,27 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BASE</t>
+          <t>人力资源和社会保障部</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>多学科开放学术资源集成检索</t>
+          <t>主管就业、社保与人事人才工作。</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>学术,搜索</t>
+          <t>政务,人社,社保</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>访问官网 - www.base-search.net</t>
+          <t>访问官网 - www.mohrss.gov.cn</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.base-search.net/</t>
+          <t>https://www.mohrss.gov.cn</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -2866,17 +2886,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>学术搜索</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2884,27 +2904,27 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>自然资源部</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>预印本学术论文检索库</t>
+          <t>主管自然资源调查、规划与确权登记。</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>学术,论文</t>
+          <t>政务,自然资源,国土</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>访问官网 - arxiv.org</t>
+          <t>访问官网 - www.mnr.gov.cn</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://arxiv.org/</t>
+          <t>https://www.mnr.gov.cn</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -2916,17 +2936,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>学术搜索</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -2934,27 +2954,27 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PubMed</t>
+          <t>生态环境部</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>生物医学论文免费检索数据库</t>
+          <t>主管生态环境保护的监督管理。</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>学术,医学</t>
+          <t>政务,生态环境,环保</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>访问官网 - pubmed.ncbi.nlm.nih.gov</t>
+          <t>访问官网 - www.mee.gov.cn</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/</t>
+          <t>https://www.mee.gov.cn</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -2966,17 +2986,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>学术搜索</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -2984,27 +3004,27 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>万方数据</t>
+          <t>住房和城乡建设部</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>大型学术文献与学位论文数据库</t>
+          <t>主管住房保障与城乡建设，发布建筑市场与市政建设政策。</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>学术,数据库</t>
+          <t>政务,住建,城乡建设</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>访问官网 - www.wanfangdata.com.cn</t>
+          <t>访问官网 - www.mohurd.gov.cn</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.wanfangdata.com.cn/</t>
+          <t>https://www.mohurd.gov.cn</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -3016,17 +3036,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>学术搜索</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -3034,27 +3054,27 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>DOAJ</t>
+          <t>交通运输部</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>开放获取期刊目录检索</t>
+          <t>主管公路、水路、铁路等综合交通运输。</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>学术,期刊</t>
+          <t>政务,交通,运输</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>访问官网 - doaj.org</t>
+          <t>访问官网 - www.mot.gov.cn</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://doaj.org/</t>
+          <t>https://www.mot.gov.cn</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -3066,17 +3086,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>学术搜索</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -3084,27 +3104,27 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AMiner</t>
+          <t>水利部</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>科技情报大数据挖掘与检索平台</t>
+          <t>主管水资源管理与水利建设，发布防汛抗旱与河湖治理信息。</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>学术,搜索</t>
+          <t>政务,水利,水资源</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>访问官网 - www.aminer.cn</t>
+          <t>访问官网 - www.mwr.gov.cn</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.aminer.cn/</t>
+          <t>https://www.mwr.gov.cn</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -3116,17 +3136,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>学术搜索</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -3134,27 +3154,27 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CiteSeerX</t>
+          <t>农业农村部</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>计算机与信息科学搜索引擎</t>
+          <t>主管农业农村发展，发布乡村振兴、农业政策与农技信息。</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>学术,搜索</t>
+          <t>政务,农业,农业农村</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>访问官网 - citeseer.ist.psu.edu</t>
+          <t>访问官网 - www.moa.gov.cn</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://citeseer.ist.psu.edu/</t>
+          <t>https://www.moa.gov.cn</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -3166,17 +3186,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>学术搜索</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -3184,27 +3204,27 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ScienceDirect</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>科技文献与期刊检索平台</t>
+          <t>主管国内外贸易与国际经贸合作，发布商务政策与市场信息。</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>学术,数据库</t>
+          <t>政务,商务,对外贸易</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>访问官网 - www.sciencedirect.com</t>
+          <t>访问官网 - www.mofcom.gov.cn</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/</t>
+          <t>https://www.mofcom.gov.cn</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -3216,17 +3236,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>AI 对话</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -3234,27 +3254,27 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>文化和旅游部</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>OpenAI 推出的通用对话式 AI 助手,支持问答、写作、编程与数据分析</t>
+          <t>主管文化事业与旅游发展，发布文旅政策与公共服务信息。</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AI对话,人工智能助手</t>
+          <t>政务,文旅,文化旅游</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>开始对话 - chat.openai.com</t>
+          <t>访问官网 - www.mct.gov.cn</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://chat.openai.com/</t>
+          <t>https://www.mct.gov.cn</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -3266,17 +3286,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AI 对话</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -3284,27 +3304,27 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>国家卫生健康委员会</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>深度求索推出的国产大模型对话助手,推理与代码能力突出</t>
+          <t>主管国民健康与医疗卫生，发布卫生政策与健康服务信息。</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>AI对话,国产大模型</t>
+          <t>政务,卫健,卫生健康</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>开始对话 - chat.deepseek.com</t>
+          <t>访问官网 - www.nhc.gov.cn</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://chat.deepseek.com/</t>
+          <t>https://www.nhc.gov.cn</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -3316,17 +3336,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>AI 对话</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -3334,27 +3354,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Claude</t>
+          <t>退役军人事务部</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Anthropic 出品的对话 AI,长文本处理与安全对齐表现出色</t>
+          <t>主管退役军人优抚安置与服务保障，维护军人军属权益。</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>AI对话,人工智能助手</t>
+          <t>政务,退役军人,优抚安置</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>开始对话 - claude.ai</t>
+          <t>访问官网 - www.mva.gov.cn</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://claude.ai/</t>
+          <t>https://www.mva.gov.cn</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -3366,17 +3386,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AI 对话</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -3384,27 +3404,27 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>应急管理部</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Google 多模态对话 AI,整合搜索与生产力工具</t>
+          <t>主管安全生产与应急救援，发布防灾减灾与事故处置信息。</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>AI对话,多模态</t>
+          <t>政务,应急,安全生产</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>开始对话 - gemini.google.com</t>
+          <t>访问官网 - www.mem.gov.cn</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://gemini.google.com/</t>
+          <t>https://www.mem.gov.cn</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -3416,17 +3436,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>AI 对话</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -3434,27 +3454,27 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>文心一言</t>
+          <t>中国人民银行</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>百度文心大模型对话助手(现文小言),中文理解与创作能力强</t>
+          <t>中央银行，制定货币政策，维护金融稳定与人民币管理。</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>AI对话,国产大模型</t>
+          <t>政务,央行,货币政策</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>开始对话 - yiyan.baidu.com</t>
+          <t>访问官网 - www.pbc.gov.cn</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://yiyan.baidu.com/</t>
+          <t>https://www.pbc.gov.cn</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -3466,17 +3486,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AI 对话</t>
+          <t>组成部门</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -3484,27 +3504,27 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kimi</t>
+          <t>审计署</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>月之暗面长上下文对话助手,擅长长文档阅读与总结</t>
+          <t>主管国家财政收支审计监督，发布审计结果与整改信息。</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>AI对话,长文本</t>
+          <t>政务,审计,审计监督</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>开始对话 - kimi.moonshot.cn</t>
+          <t>访问官网 - www.audit.gov.cn</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://kimi.moonshot.cn/</t>
+          <t>https://www.audit.gov.cn</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -3516,17 +3536,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AI 对话</t>
+          <t>综合搜索</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -3534,27 +3554,27 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>豆包</t>
+          <t>Google 搜索</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>字节跳动推出的综合对话 AI 助手,覆盖问答与创作</t>
+          <t>谷歌搜索引擎，全球索引量最大的多语综合搜索，学术、地图、翻译等延伸服务齐全</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>AI对话,国产大模型</t>
+          <t>搜索引擎,聚合搜索</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>开始对话 - www.doubao.com</t>
+          <t>访问官网 - www.google.com</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://www.doubao.com/</t>
+          <t>https://www.google.com</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -3566,17 +3586,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AI 对话</t>
+          <t>综合搜索</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -3584,27 +3604,27 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>通义千问</t>
+          <t>必应 Bing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>阿里通义系列大模型对话助手,支持多模态与 Agent</t>
+          <t>微软旗下综合搜索，深度集成 Windows 与 Copilot AI 智能应答</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>AI对话,国产大模型</t>
+          <t>搜索引擎,聚合搜索</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>开始对话 - tongyi.aliyun.com</t>
+          <t>访问官网 - www.bing.com</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://tongyi.aliyun.com/</t>
+          <t>https://www.bing.com</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -3616,17 +3636,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AI 对话</t>
+          <t>综合搜索</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -3634,27 +3654,27 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>智谱清言</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>智谱 AI 的 GLM 大模型对话助手,推理与工具调用均衡</t>
+          <t>中文网页与语义理解见长，贴吧、知道、百科构成内容生态闭环</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>AI对话,国产大模型</t>
+          <t>搜索引擎,聚合搜索</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>开始对话 - chatglm.cn</t>
+          <t>访问官网 - www.baidu.com</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://chatglm.cn/</t>
+          <t>https://www.baidu.com</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -3666,17 +3686,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>AI 对话</t>
+          <t>购物</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -3684,27 +3704,27 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Copilot</t>
+          <t>淘宝</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>微软 AI 对话助手,深度集成 Windows 与 Office 生产力</t>
+          <t>电商商品与店铺检索，支持销量、价格、信用筛选与直播带货</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>AI对话,生产力</t>
+          <t>搜索引擎,聚合搜索</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>开始对话 - copilot.microsoft.com</t>
+          <t>访问官网 - www.taobao.com</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://copilot.microsoft.com/</t>
+          <t>https://www.taobao.com</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -3716,17 +3736,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>AI 对话</t>
+          <t>购物</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -3734,27 +3754,27 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Meta AI</t>
+          <t>京东</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Meta 推出的通用对话 AI 助手,跨社交平台可用</t>
+          <t>自营与品牌电商检索，以物流时效与正品保障为特色的购物搜索</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>AI对话,人工智能助手</t>
+          <t>搜索引擎,聚合搜索</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>开始对话 - www.meta.ai</t>
+          <t>访问官网 - www.jd.com</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://www.meta.ai/</t>
+          <t>https://www.jd.com</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -3766,17 +3786,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AI 对话</t>
+          <t>购物</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -3784,27 +3804,27 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grok</t>
+          <t>拼多多</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>xAI 推出的对话 AI,接入 X 平台实时信息</t>
+          <t>低价拼团模式下的商品搜索，下沉市场供给与农货丰富</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>AI对话,实时</t>
+          <t>搜索引擎,聚合搜索</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>开始对话 - grok.com</t>
+          <t>访问官网 - mobile.yangkeduo.com</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://grok.com/</t>
+          <t>https://mobile.yangkeduo.com</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -3816,17 +3836,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AI 对话</t>
+          <t>社区知识</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -3834,27 +3854,27 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Poe</t>
+          <t>知乎</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Quora 聚合多模型的对话平台,可一键切换不同 AI</t>
+          <t>高质量中文问答社区，专业答主长文与观点检索入口</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>AI对话,聚合</t>
+          <t>搜索引擎,聚合搜索</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>开始对话 - poe.com</t>
+          <t>访问官网 - www.zhihu.com</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://poe.com/</t>
+          <t>https://www.zhihu.com</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -3866,17 +3886,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>directory/engine</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AI 对话</t>
+          <t>社区知识</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -3884,27 +3904,27 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pi</t>
+          <t>维基百科</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Inflection 出品的温和陪伴型对话助手,侧重自然交流</t>
+          <t>非营利的协作百科，引用可追溯、跨语言词条互链</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>AI对话,陪伴</t>
+          <t>搜索引擎,聚合搜索</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>开始对话 - pi.ai</t>
+          <t>访问官网 - zh.wikipedia.org</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://pi.ai/</t>
+          <t>https://zh.wikipedia.org</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -3916,17 +3936,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>社区知识</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -3934,27 +3954,27 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>全国人民代表大会</t>
+          <t>微信搜一搜</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>最高国家权力机关，行使国家立法权，官方网站发布法律、公报与常委会信息。</t>
+          <t>检索公众号文章、视频号与朋友圈内容，封闭生态内搜索</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>人大,全国人大,国家立法</t>
+          <t>搜索引擎,聚合搜索</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>访问官网 - www.npc.gov.cn</t>
+          <t>访问官网 - weixin.sogou.com</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://www.npc.gov.cn</t>
+          <t>https://weixin.sogou.com</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -3966,17 +3986,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>直辖市</t>
+          <t>社区知识</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -3984,27 +4004,27 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>北京市人民代表大会常务委员会</t>
+          <t>头条搜索</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>北京市人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
+          <t>基于字节推荐算法的通用搜索，信息流与热点聚合</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>人大,北京,直辖市</t>
+          <t>搜索引擎,聚合搜索</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>访问官网 - www.bjrd.gov.cn</t>
+          <t>访问官网 - so.toutiao.com</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://www.bjrd.gov.cn</t>
+          <t>https://so.toutiao.com</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -4016,17 +4036,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>直辖市</t>
+          <t>视频</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -4034,27 +4054,27 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>上海市人民代表大会常务委员会</t>
+          <t>哔哩哔哩</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>上海市人民代表大会常设机关，地方立法与监督工作平台。</t>
+          <t>ACG 与 UP 主视频检索，弹幕文化与番剧社区入口</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>人大,上海,直辖市</t>
+          <t>搜索引擎,聚合搜索</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>访问官网 - www.shrd.gov.cn</t>
+          <t>访问官网 - www.bilibili.com</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://www.shrd.gov.cn</t>
+          <t>https://www.bilibili.com</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -4066,17 +4086,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>直辖市</t>
+          <t>视频</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -4084,27 +4104,27 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>天津市人民代表大会常务委员会</t>
+          <t>抖音</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>天津市人民代表大会常设机关，发布地方性法规与监督信息。</t>
+          <t>短视频内容搜索，按热点与挑战标签分发与发现</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>人大,天津,直辖市</t>
+          <t>搜索引擎,聚合搜索</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>访问官网 - www.tjrd.gov.cn</t>
+          <t>访问官网 - www.douyin.com</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://www.tjrd.gov.cn</t>
+          <t>https://www.douyin.com</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -4116,17 +4136,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>直辖市</t>
+          <t>开发</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -4134,27 +4154,27 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>重庆市人民代表大会常务委员会</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>重庆市人民代表大会常设机关，地方立法与代表工作平台。</t>
+          <t>代码仓库与开源项目检索，支持 Issue、PR 与代码全文搜索</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>人大,重庆,直辖市</t>
+          <t>搜索引擎,聚合搜索</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>访问官网 - www.cqrd.gov.cn</t>
+          <t>访问官网 - github.com</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://www.cqrd.gov.cn</t>
+          <t>https://github.com</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -4166,17 +4186,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>开发</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -4184,27 +4204,27 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>河北省人民代表大会常务委员会</t>
+          <t>Stack Overflow</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>河北省人民代表大会常设机关，发布地方立法、监督与代表履职信息。</t>
+          <t>编程报错与技术方案问答检索，按投票质量排序</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>人大,河北,省</t>
+          <t>搜索引擎,聚合搜索</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>访问官网 - www.hbrd.gov.cn</t>
+          <t>访问官网 - stackoverflow.com</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://www.hbrd.gov.cn</t>
+          <t>https://stackoverflow.com</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -4216,17 +4236,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>开发</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -4234,27 +4254,27 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>山西省人民代表大会常务委员会</t>
+          <t>掘金</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>山西省人民代表大会常设机关，发布地方性法规与监督工作信息。</t>
+          <t>前端、客户端与后端技术文章、教程与专栏检索</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>人大,山西,省</t>
+          <t>搜索引擎,聚合搜索</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>访问官网 - www.sxpc.gov.cn</t>
+          <t>访问官网 - juejin.cn</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://www.sxpc.gov.cn</t>
+          <t>https://juejin.cn</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -4266,17 +4286,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -4284,27 +4304,27 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>辽宁省人民代表大会常务委员会</t>
+          <t>高德地图</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>辽宁省人民代表大会常设机关，发布地方立法与代表工作信息。</t>
+          <t>POI 地点、路线与实时路况检索，含打车与周边服务</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>人大,辽宁,省</t>
+          <t>搜索引擎,聚合搜索</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>访问官网 - www.lnrd.gov.cn</t>
+          <t>访问官网 - www.amap.com</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://www.lnrd.gov.cn</t>
+          <t>https://www.amap.com</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -4316,17 +4336,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -4334,27 +4354,27 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>吉林省人民代表大会常务委员会</t>
+          <t>有道翻译</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>吉林省人民代表大会常设机关，发布地方性法规与监督信息。</t>
+          <t>中英及多语词典与整句翻译，支持文档与网页翻译</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>人大,吉林,省</t>
+          <t>搜索引擎,聚合搜索</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>访问官网 - www.jlrd.gov.cn</t>
+          <t>访问官网 - www.youdao.com</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://www.jlrd.gov.cn</t>
+          <t>https://www.youdao.com</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -4366,17 +4386,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -4384,27 +4404,27 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>黑龙江省人民代表大会常务委员会</t>
+          <t>网易云音乐</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>黑龙江省人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
+          <t>歌曲、歌单与歌词检索推荐，以乐评社区为特色</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>人大,黑龙江,省</t>
+          <t>搜索引擎,聚合搜索</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>访问官网 - www.hljrd.gov.cn</t>
+          <t>访问官网 - music.163.com</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://www.hljrd.gov.cn</t>
+          <t>https://music.163.com</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -4416,17 +4436,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>数据库</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -4434,27 +4454,22 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>江苏省人民代表大会常务委员会</t>
+          <t>在线读报</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>江苏省人民代表大会常设机关，地方立法与监督工作平台。</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>人大,江苏,省</t>
+          <t>九星时代报刊在线系统包含了综合报、晨报、日报、晚报、都市报、经济报、生活报、法制报、农业报、军事报、体育报、青少年、保健报和其他14大类的报纸资源，可以充分的满足不同用户的阅读需求。 使用指南 缩放功能 单击报纸任何一点，便可将报纸整版放大，同理单击放大后的报纸任意一处，即可缩小。同时也可用右侧操作项进行放大缩小。拖动功能 ：当报纸放大后，手指可随意拖动整版报纸，将超出显示区位置的报纸托动至显示区内。翻页功能：点住报纸画面，向左或向右横向滑动，即可将报纸翻页。</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>访问官网 - www.jsrd.gov.cn</t>
+          <t>访问首页 - 202.106.125.196</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://www.jsrd.gov.cn</t>
+          <t>http://202.106.125.196</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -4466,17 +4481,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>143</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>数据库</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -4484,27 +4499,17 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>浙江省人民代表大会常务委员会</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>浙江省人民代表大会常设机关，发布地方性法规与代表信息。</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>人大,浙江,省</t>
+          <t>国务院政策文件库</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>访问官网 - www.zjrd.gov.cn</t>
+          <t>访问官网 - sousuo.www.gov.cn/zcwjk/</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://www.zjrd.gov.cn</t>
+          <t>https://sousuo.www.gov.cn/zcwjk/</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -4516,17 +4521,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>144</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>综合搜索</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -4534,27 +4539,27 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>安徽省人民代表大会常务委员会</t>
+          <t>DuckDuckGo</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>安徽省人民代表大会常设机关，发布地方立法与代表履职信息。</t>
+          <t>隐私搜索引擎，不收集用户信息、无广告</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>人大,安徽,省</t>
+          <t>搜索引擎,隐私</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>访问官网 - www.ahrd.gov.cn</t>
+          <t>访问官网 - duckduckgo.com</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://www.ahrd.gov.cn</t>
+          <t>https://duckduckgo.com/</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -4566,17 +4571,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>145</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>综合搜索</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -4584,27 +4589,27 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>福建省人民代表大会常务委员会</t>
+          <t>Yandex</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>福建省人民代表大会常设机关，发布地方性法规与监督工作信息。</t>
+          <t>俄罗斯主流综合搜索引擎</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>人大,福建,省</t>
+          <t>搜索引擎</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>访问官网 - www.fjrd.gov.cn</t>
+          <t>访问官网 - yandex.com</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://www.fjrd.gov.cn</t>
+          <t>https://yandex.com/</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -4616,17 +4621,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>146</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>综合搜索</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -4634,27 +4639,27 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>江西省人民代表大会常务委员会</t>
+          <t>Qwant</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>江西省人民代表大会常设机关，发布地方立法与代表工作信息。</t>
+          <t>法国搜索引擎，注重隐私保护</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>人大,江西,省</t>
+          <t>搜索引擎,隐私</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>访问官网 - www.jxrd.gov.cn</t>
+          <t>访问官网 - www.qwant.com</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://www.jxrd.gov.cn</t>
+          <t>https://www.qwant.com/</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -4666,17 +4671,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>147</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>综合搜索</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -4684,27 +4689,27 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>山东省人民代表大会常务委员会</t>
+          <t>Perplexity</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>山东省人民代表大会常设机关，地方立法与监督工作平台。</t>
+          <t>对话式 AI 搜索引擎，直接给出带引用的答案</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>人大,山东,省</t>
+          <t>搜索引擎,AI搜索</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>访问官网 - www.sdrd.gov.cn</t>
+          <t>访问官网 - www.perplexity.ai</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://www.sdrd.gov.cn</t>
+          <t>https://www.perplexity.ai/</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -4716,17 +4721,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>148</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>综合搜索</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -4734,27 +4739,27 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>河南省人民代表大会常务委员会</t>
+          <t>You.com</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>河南省人民代表大会常设机关，发布地方性法规与监督信息。</t>
+          <t>AI 搜索引擎，整合多模型结果并支持对话</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>人大,河南,省</t>
+          <t>搜索引擎,AI搜索</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>访问官网 - www.henanrd.gov.cn</t>
+          <t>访问官网 - you.com</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://www.henanrd.gov.cn</t>
+          <t>https://you.com/</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -4766,17 +4771,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>149</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>综合搜索</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -4784,27 +4789,27 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>湖北省人民代表大会常务委员会</t>
+          <t>Felo</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>湖北省人民代表大会常设机关，地方立法与代表工作平台。</t>
+          <t>免费 AI 智能搜索引擎，支持多语问答</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>人大,湖北,省</t>
+          <t>搜索引擎,AI搜索</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>访问官网 - www.hppc.gov.cn</t>
+          <t>访问官网 - felo.ai</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://www.hppc.gov.cn</t>
+          <t>https://felo.ai/search</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -4816,17 +4821,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>150</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>社区知识</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -4834,27 +4839,27 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>湖南省人民代表大会常务委员会</t>
+          <t>知乎搜索</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>湖南省人民代表大会常设机关，发布地方性法规与监督信息。</t>
+          <t>搜索知乎站内的问答与文章</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>人大,湖南,省</t>
+          <t>搜索引擎,社区</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>访问官网 - www.hnrd.gov.cn</t>
+          <t>访问官网 - zhihu.sogou.com</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://www.hnrd.gov.cn</t>
+          <t>https://zhihu.sogou.com/</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -4866,17 +4871,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>社区知识</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -4884,27 +4889,27 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>广东省人民代表大会常务委员会</t>
+          <t>WikiHow</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>广东省人民代表大会常设机关，发布地方性法规与监督信息。</t>
+          <t>综合技能与万事指南搜索站</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>人大,广东,省</t>
+          <t>知识,指南</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>访问官网 - www.rd.gd.cn</t>
+          <t>访问官网 - zh.wikihow.com</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://www.rd.gd.cn</t>
+          <t>https://zh.wikihow.com/</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -4916,17 +4921,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>152</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>开发</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -4934,27 +4939,27 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>海南省人民代表大会常务委员会</t>
+          <t>开发者搜索</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>海南省人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
+          <t>百度面向开发者的垂直搜索引擎</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>人大,海南,省</t>
+          <t>搜索引擎,开发</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>访问官网 - www.hainanpc.gov.cn</t>
+          <t>访问官网 - kaifa.baidu.com</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://www.hainanpc.gov.cn</t>
+          <t>https://kaifa.baidu.com/</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -4966,17 +4971,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>153</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -4984,27 +4989,27 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>四川省人民代表大会常务委员会</t>
+          <t>TinEye</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>四川省人民代表大会常设机关，发布地方性法规与监督信息。</t>
+          <t>以图搜图的反向图片检索搜索引擎</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>人大,四川,省</t>
+          <t>以图搜图,工具</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>访问官网 - www.scspc.gov.cn</t>
+          <t>访问官网 - www.tineye.com</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://www.scspc.gov.cn</t>
+          <t>https://www.tineye.com</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -5016,17 +5021,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>154</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -5034,27 +5039,27 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>贵州省人民代表大会常务委员会</t>
+          <t>网站历史快照</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>贵州省人民代表大会常设机关，发布地方性法规与监督信息。</t>
+          <t>Internet Archive 查看网站历史存档快照</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>人大,贵州,省</t>
+          <t>工具,归档</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>访问官网 - www.gzrd.gov.cn</t>
+          <t>访问官网 - archive.org</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://www.gzrd.gov.cn</t>
+          <t>https://archive.org/</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -5066,17 +5071,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>155</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -5084,27 +5089,27 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>云南省人民代表大会常务委员会</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>云南省人民代表大会常设机关，发布地方立法与代表履职信息。</t>
+          <t>查看并分析任意网站的流量与排名</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>人大,云南,省</t>
+          <t>工具,分析</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>访问官网 - www.ynrd.gov.cn</t>
+          <t>访问官网 - www.similarweb.com</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://www.ynrd.gov.cn</t>
+          <t>https://www.similarweb.com/zh/</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -5116,17 +5121,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>156</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -5134,27 +5139,27 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>陕西省人民代表大会常务委员会</t>
+          <t>相似网站</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>陕西省人民代表大会常设机关，发布地方性法规与监督工作信息。</t>
+          <t>寻找功能相似的网站推荐</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>人大,陕西,省</t>
+          <t>工具,发现</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>访问官网 - www.sxrd.gov.cn</t>
+          <t>访问官网 - www.similarsitesearch.com</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://www.sxrd.gov.cn</t>
+          <t>https://www.similarsitesearch.com/</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -5166,17 +5171,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>157</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -5184,27 +5189,27 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>甘肃省人民代表大会常务委员会</t>
+          <t>Windy</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>甘肃省人民代表大会常设机关，发布地方立法与代表工作信息。</t>
+          <t>可视化天气数据与气象预报查询</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>人大,甘肃,省</t>
+          <t>工具,天气</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>访问官网 - www.gsrdw.gov.cn</t>
+          <t>访问官网 - www.windy.com</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://www.gsrdw.gov.cn</t>
+          <t>https://www.windy.com/</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -5216,17 +5221,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>158</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -5234,27 +5239,27 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>青海省人民代表大会常务委员会</t>
+          <t>Google 图书</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>青海省人民代表大会常设机关，发布地方性法规与监督信息。</t>
+          <t>检索正规出版书籍、杂志、报纸的摘要</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>人大,青海,省</t>
+          <t>图书,搜索</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>访问官网 - www.qhrd.gov.cn</t>
+          <t>访问官网 - books.google.com</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://www.qhrd.gov.cn</t>
+          <t>https://books.google.com/</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -5266,17 +5271,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>自治区</t>
+          <t>素材</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -5284,27 +5289,27 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>内蒙古自治区人民代表大会常务委员会</t>
+          <t>CC Search</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>内蒙古自治区人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
+          <t>检索可免费使用的无版权图片资源</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>人大,内蒙古,自治区</t>
+          <t>图片,素材</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>访问官网 - www.nmgrd.gov.cn</t>
+          <t>访问官网 - ccsearch.creativecommons.org</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://www.nmgrd.gov.cn</t>
+          <t>https://ccsearch.creativecommons.org/</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -5316,17 +5321,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>160</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>自治区</t>
+          <t>素材</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -5334,27 +5339,27 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>广西壮族自治区人民代表大会常务委员会</t>
+          <t>Pexels</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>广西壮族自治区人民代表大会常设机关，发布地方立法与代表履职信息。</t>
+          <t>高质量免费图片与视频素材库</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>人大,广西,自治区</t>
+          <t>图片,素材</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>访问官网 - www.gxrd.gov.cn</t>
+          <t>访问官网 - www.pexels.com</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://www.gxrd.gov.cn</t>
+          <t>https://www.pexels.com/</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -5366,17 +5371,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>161</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>自治区</t>
+          <t>素材</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -5384,27 +5389,27 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>西藏自治区人民代表大会常务委员会</t>
+          <t>Unsplash</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>西藏自治区人民代表大会常设机关，发布地方立法与监督信息。</t>
+          <t>免费高清图片素材社区</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>人大,西藏,自治区</t>
+          <t>图片,素材</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>访问官网 - www.xizangrd.gov.cn</t>
+          <t>访问官网 - unsplash.com</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://www.xizangrd.gov.cn</t>
+          <t>https://unsplash.com/</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -5416,17 +5421,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>162</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>自治区</t>
+          <t>素材</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -5434,27 +5439,27 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>宁夏回族自治区人民代表大会常务委员会</t>
+          <t>LibreStock</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>宁夏回族自治区人民代表大会常设机关，发布地方性法规与代表工作信息。</t>
+          <t>检索多家图库的优质高清图片</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>人大,宁夏,自治区</t>
+          <t>图片,素材</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>访问官网 - www.nxrd.gov.cn</t>
+          <t>访问官网 - librestock.com</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://www.nxrd.gov.cn</t>
+          <t>https://librestock.com/</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -5466,17 +5471,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>163</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>自治区</t>
+          <t>素材</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -5484,27 +5489,27 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区人民代表大会常务委员会</t>
+          <t>Iconfinder</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区人民代表大会常设机关，发布地方立法、监督与代表工作信息。</t>
+          <t>查找 logo 等矢量图标素材</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>人大,新疆,自治区</t>
+          <t>图标,素材</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>访问官网 - www.xjpcsc.gov.cn</t>
+          <t>访问官网 - www.iconfinder.com</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://www.xjpcsc.gov.cn</t>
+          <t>https://www.iconfinder.com/</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -5516,17 +5521,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>164</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>国务院</t>
+          <t>素材</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -5534,27 +5539,27 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>中华人民共和国中央人民政府（国务院）</t>
+          <t>FindIcons</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>国务院官方网站，国家政务总门户，发布政策法规与政务信息。</t>
+          <t>优秀图标素材库检索</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>政务,国务院,中央政府</t>
+          <t>图标,素材</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>访问官网 - www.gov.cn</t>
+          <t>访问官网 - findicons.com</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://www.gov.cn</t>
+          <t>https://findicons.com/</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -5566,17 +5571,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>165</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>国家平台</t>
+          <t>学术搜索</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -5584,27 +5589,27 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>国家政务服务平台</t>
+          <t>谷歌学术</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>全国统一政务服务平台，提供在线办事、政务服务与效能监督。</t>
+          <t>Google 提供的免费学术文章搜索</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>政务,服务平台,在线办事</t>
+          <t>学术,搜索</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>访问官网 - gjzwfw.www.gov.cn</t>
+          <t>访问官网 - scholar.google.com</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://gjzwfw.www.gov.cn</t>
+          <t>https://scholar.google.com/</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -5616,17 +5621,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>166</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>学术搜索</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -5634,27 +5639,27 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>外交部</t>
+          <t>百度学术</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>主管外交事务，发布外交政策、双边关系与国际交往信息。</t>
+          <t>百度学术信息搜索引擎</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>政务,外交,外交部</t>
+          <t>学术,搜索</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>访问官网 - www.mfa.gov.cn</t>
+          <t>访问官网 - xueshu.baidu.com</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://www.mfa.gov.cn</t>
+          <t>https://xueshu.baidu.com/</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -5666,17 +5671,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>167</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>学术搜索</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -5684,27 +5689,27 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>国防部</t>
+          <t>中国知网</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>中华人民共和国国防部，发布国防政策、军队建设与权威军事信息。</t>
+          <t>精品论文与学术资源检索平台</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>政务,国防,国防部</t>
+          <t>学术,数据库</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>访问官网 - www.mod.gov.cn</t>
+          <t>访问官网 - www.cnki.net</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://www.mod.gov.cn</t>
+          <t>https://www.cnki.net/</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -5716,17 +5721,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>168</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>学术搜索</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -5734,27 +5739,27 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>国家发展和改革委员会</t>
+          <t>Semantic Scholar</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>宏观经济综合管理，拟订发展战略与规划。</t>
+          <t>免费学术搜索引擎（期刊/会议资料）</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>政务,发改委,宏观经济</t>
+          <t>学术,搜索</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>访问官网 - www.ndrc.gov.cn</t>
+          <t>访问官网 - www.semanticscholar.org</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://www.ndrc.gov.cn</t>
+          <t>https://www.semanticscholar.org/</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -5766,17 +5771,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>学术搜索</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -5784,27 +5789,27 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>教育部</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>主管教育事业与语言文字工作，发布教育政策。</t>
+          <t>多学科开放学术资源集成检索</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>政务,教育,教育部</t>
+          <t>学术,搜索</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>访问官网 - www.moe.gov.cn</t>
+          <t>访问官网 - www.base-search.net</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://www.moe.gov.cn</t>
+          <t>https://www.base-search.net/</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -5816,17 +5821,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>170</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>学术搜索</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -5834,27 +5839,27 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>科学技术部</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>主管科技发展与创新，发布科技政策与研发计划信息。</t>
+          <t>预印本学术论文检索库</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>政务,科技,科技部</t>
+          <t>学术,论文</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>访问官网 - www.most.gov.cn</t>
+          <t>访问官网 - arxiv.org</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://www.most.gov.cn</t>
+          <t>https://arxiv.org/</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -5866,17 +5871,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>171</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>学术搜索</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -5884,27 +5889,27 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>工业和信息化部</t>
+          <t>PubMed</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>主管工业与信息化产业发展与行业管理。</t>
+          <t>生物医学论文免费检索数据库</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>政务,工信,信息化</t>
+          <t>学术,医学</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>访问官网 - www.miit.gov.cn</t>
+          <t>访问官网 - pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://www.miit.gov.cn</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -5916,17 +5921,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>172</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>学术搜索</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -5934,27 +5939,27 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>国家民族事务委员会</t>
+          <t>万方数据</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>主管民族事务与民族团结进步工作，发布民族政策信息。</t>
+          <t>大型学术文献与学位论文数据库</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>政务,民委,民族事务</t>
+          <t>学术,数据库</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>访问官网 - www.neac.gov.cn</t>
+          <t>访问官网 - www.wanfangdata.com.cn</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://www.neac.gov.cn</t>
+          <t>https://www.wanfangdata.com.cn/</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -5966,17 +5971,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>173</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>学术搜索</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -5984,27 +5989,27 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>公安部</t>
+          <t>DOAJ</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>维护社会治安，主管公安工作。</t>
+          <t>开放获取期刊目录检索</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>政务,公安,公安部</t>
+          <t>学术,期刊</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>访问官网 - www.mps.gov.cn</t>
+          <t>访问官网 - doaj.org</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://www.mps.gov.cn</t>
+          <t>https://doaj.org/</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -6016,17 +6021,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>学术搜索</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -6034,27 +6039,27 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>民政部</t>
+          <t>AMiner</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>主管民政事务、社会救助与社会组织管理。</t>
+          <t>科技情报大数据挖掘与检索平台</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>政务,民政,民政部</t>
+          <t>学术,搜索</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>访问官网 - www.mca.gov.cn</t>
+          <t>访问官网 - www.aminer.cn</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://www.mca.gov.cn</t>
+          <t>https://www.aminer.cn/</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -6066,17 +6071,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>175</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>学术搜索</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -6084,27 +6089,27 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>司法部</t>
+          <t>CiteSeerX</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>主管司法行政、法治建设与法律服务。</t>
+          <t>计算机与信息科学搜索引擎</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>政务,司法,司法部</t>
+          <t>学术,搜索</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>访问官网 - www.moj.gov.cn</t>
+          <t>访问官网 - citeseer.ist.psu.edu</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://www.moj.gov.cn</t>
+          <t>https://citeseer.ist.psu.edu/</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -6116,17 +6121,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>176</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>学术搜索</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -6134,27 +6139,27 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>财政部</t>
+          <t>ScienceDirect</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>主管国家财政收支与财税政策。</t>
+          <t>科技文献与期刊检索平台</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>政务,财政,财政部</t>
+          <t>学术,数据库</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>访问官网 - www.mof.gov.cn</t>
+          <t>访问官网 - www.sciencedirect.com</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://www.mof.gov.cn</t>
+          <t>https://www.sciencedirect.com/</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -6166,17 +6171,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>177</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>AI 对话</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -6184,27 +6189,27 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>人力资源和社会保障部</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>主管就业、社保与人事人才工作。</t>
+          <t>OpenAI 推出的通用对话式 AI 助手,支持问答、写作、编程与数据分析</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>政务,人社,社保</t>
+          <t>AI对话,人工智能助手</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>访问官网 - www.mohrss.gov.cn</t>
+          <t>开始对话 - chat.openai.com</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://www.mohrss.gov.cn</t>
+          <t>https://chat.openai.com/</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -6216,17 +6221,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>AI 对话</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -6234,27 +6239,27 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>自然资源部</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>主管自然资源调查、规划与确权登记。</t>
+          <t>深度求索推出的国产大模型对话助手,推理与代码能力突出</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>政务,自然资源,国土</t>
+          <t>AI对话,国产大模型</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>访问官网 - www.mnr.gov.cn</t>
+          <t>开始对话 - chat.deepseek.com</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://www.mnr.gov.cn</t>
+          <t>https://chat.deepseek.com/</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -6266,17 +6271,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>AI 对话</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -6284,27 +6289,27 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>生态环境部</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>主管生态环境保护的监督管理。</t>
+          <t>Anthropic 出品的对话 AI,长文本处理与安全对齐表现出色</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>政务,生态环境,环保</t>
+          <t>AI对话,人工智能助手</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>访问官网 - www.mee.gov.cn</t>
+          <t>开始对话 - claude.ai</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://www.mee.gov.cn</t>
+          <t>https://claude.ai/</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -6316,17 +6321,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>180</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>AI 对话</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -6334,27 +6339,27 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>住房和城乡建设部</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>主管住房保障与城乡建设，发布建筑市场与市政建设政策。</t>
+          <t>Google 多模态对话 AI,整合搜索与生产力工具</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>政务,住建,城乡建设</t>
+          <t>AI对话,多模态</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>访问官网 - www.mohurd.gov.cn</t>
+          <t>开始对话 - gemini.google.com</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://www.mohurd.gov.cn</t>
+          <t>https://gemini.google.com/</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -6366,17 +6371,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>181</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>AI 对话</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -6384,27 +6389,27 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>交通运输部</t>
+          <t>文心一言</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>主管公路、水路、铁路等综合交通运输。</t>
+          <t>百度文心大模型对话助手(现文小言),中文理解与创作能力强</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>政务,交通,运输</t>
+          <t>AI对话,国产大模型</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>访问官网 - www.mot.gov.cn</t>
+          <t>开始对话 - yiyan.baidu.com</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://www.mot.gov.cn</t>
+          <t>https://yiyan.baidu.com/</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -6416,17 +6421,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>182</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>AI 对话</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -6434,27 +6439,27 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>水利部</t>
+          <t>Kimi</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>主管水资源管理与水利建设，发布防汛抗旱与河湖治理信息。</t>
+          <t>月之暗面长上下文对话助手,擅长长文档阅读与总结</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>政务,水利,水资源</t>
+          <t>AI对话,长文本</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>访问官网 - www.mwr.gov.cn</t>
+          <t>开始对话 - kimi.moonshot.cn</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://www.mwr.gov.cn</t>
+          <t>https://kimi.moonshot.cn/</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -6466,17 +6471,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>183</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>AI 对话</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -6484,27 +6489,27 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>农业农村部</t>
+          <t>豆包</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>主管农业农村发展，发布乡村振兴、农业政策与农技信息。</t>
+          <t>字节跳动推出的综合对话 AI 助手,覆盖问答与创作</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>政务,农业,农业农村</t>
+          <t>AI对话,国产大模型</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>访问官网 - www.moa.gov.cn</t>
+          <t>开始对话 - www.doubao.com</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://www.moa.gov.cn</t>
+          <t>https://www.doubao.com/</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -6516,17 +6521,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>184</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>AI 对话</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -6534,27 +6539,27 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>通义千问</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>主管国内外贸易与国际经贸合作，发布商务政策与市场信息。</t>
+          <t>阿里通义系列大模型对话助手,支持多模态与 Agent</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>政务,商务,对外贸易</t>
+          <t>AI对话,国产大模型</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>访问官网 - www.mofcom.gov.cn</t>
+          <t>开始对话 - tongyi.aliyun.com</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://www.mofcom.gov.cn</t>
+          <t>https://tongyi.aliyun.com/</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -6566,17 +6571,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>185</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>AI 对话</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -6584,27 +6589,27 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>文化和旅游部</t>
+          <t>智谱清言</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>主管文化事业与旅游发展，发布文旅政策与公共服务信息。</t>
+          <t>智谱 AI 的 GLM 大模型对话助手,推理与工具调用均衡</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>政务,文旅,文化旅游</t>
+          <t>AI对话,国产大模型</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>访问官网 - www.mct.gov.cn</t>
+          <t>开始对话 - chatglm.cn</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://www.mct.gov.cn</t>
+          <t>https://chatglm.cn/</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -6616,17 +6621,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>186</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>AI 对话</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -6634,27 +6639,27 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>国家卫生健康委员会</t>
+          <t>Copilot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>主管国民健康与医疗卫生，发布卫生政策与健康服务信息。</t>
+          <t>微软 AI 对话助手,深度集成 Windows 与 Office 生产力</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>政务,卫健,卫生健康</t>
+          <t>AI对话,生产力</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>访问官网 - www.nhc.gov.cn</t>
+          <t>开始对话 - copilot.microsoft.com</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>https://www.nhc.gov.cn</t>
+          <t>https://copilot.microsoft.com/</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -6666,17 +6671,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>187</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>AI 对话</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -6684,27 +6689,27 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>退役军人事务部</t>
+          <t>Meta AI</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>主管退役军人优抚安置与服务保障，维护军人军属权益。</t>
+          <t>Meta 推出的通用对话 AI 助手,跨社交平台可用</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>政务,退役军人,优抚安置</t>
+          <t>AI对话,人工智能助手</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>访问官网 - www.mva.gov.cn</t>
+          <t>开始对话 - www.meta.ai</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>https://www.mva.gov.cn</t>
+          <t>https://www.meta.ai/</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -6716,17 +6721,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>188</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>AI 对话</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -6734,27 +6739,27 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>应急管理部</t>
+          <t>Grok</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>主管安全生产与应急救援，发布防灾减灾与事故处置信息。</t>
+          <t>xAI 推出的对话 AI,接入 X 平台实时信息</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>政务,应急,安全生产</t>
+          <t>AI对话,实时</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>访问官网 - www.mem.gov.cn</t>
+          <t>开始对话 - grok.com</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>https://www.mem.gov.cn</t>
+          <t>https://grok.com/</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -6766,17 +6771,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>189</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>AI 对话</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -6784,27 +6789,27 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>中国人民银行</t>
+          <t>Poe</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>中央银行，制定货币政策，维护金融稳定与人民币管理。</t>
+          <t>Quora 聚合多模型的对话平台,可一键切换不同 AI</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>政务,央行,货币政策</t>
+          <t>AI对话,聚合</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>访问官网 - www.pbc.gov.cn</t>
+          <t>开始对话 - poe.com</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>https://www.pbc.gov.cn</t>
+          <t>https://poe.com/</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -6816,17 +6821,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>190</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/search</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>组成部门</t>
+          <t>AI 对话</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -6834,27 +6839,27 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>审计署</t>
+          <t>Pi</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>主管国家财政收支审计监督，发布审计结果与整改信息。</t>
+          <t>Inflection 出品的温和陪伴型对话助手,侧重自然交流</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>政务,审计,审计监督</t>
+          <t>AI对话,陪伴</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>访问官网 - www.audit.gov.cn</t>
+          <t>开始对话 - pi.ai</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>https://www.audit.gov.cn</t>
+          <t>https://pi.ai/</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -6876,7 +6881,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>全国政协</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -7491,7 +7496,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -7551,7 +7556,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -7611,7 +7616,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -7671,7 +7676,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -7731,7 +7736,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -7796,7 +7801,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E143" t="n">
@@ -7856,7 +7861,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -7916,7 +7921,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -7976,7 +7981,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -8036,7 +8041,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -8096,7 +8101,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -8156,7 +8161,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E149" t="n">
@@ -8216,7 +8221,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -8276,7 +8281,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E151" t="n">
@@ -8336,7 +8341,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -8396,7 +8401,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -8461,7 +8466,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -8526,7 +8531,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -8586,7 +8591,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -8646,7 +8651,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -8706,7 +8711,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -8766,7 +8771,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -8826,7 +8831,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -8886,7 +8891,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -8946,7 +8951,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -9006,7 +9011,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -9066,7 +9071,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -9126,7 +9131,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E165" t="n">
@@ -9186,7 +9191,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -9246,7 +9251,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -9306,7 +9311,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>省级政协</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -9366,7 +9371,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>副省级城市政协</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -9421,7 +9426,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>副省级城市政协</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -9471,7 +9476,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -9521,7 +9526,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -9571,7 +9576,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>县级政协</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -9626,7 +9631,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -9676,7 +9681,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -9726,7 +9731,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -9776,7 +9781,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -9826,7 +9831,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -9876,7 +9881,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -9926,7 +9931,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -9976,7 +9981,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -10026,7 +10031,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -10076,7 +10081,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -10126,7 +10131,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -10181,7 +10186,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -10231,7 +10236,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -10281,7 +10286,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -10331,7 +10336,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -10381,7 +10386,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -10431,7 +10436,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>副省级城市政协</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -10481,7 +10486,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>副省级城市政协</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -10531,7 +10536,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>相关机构</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -10596,7 +10601,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>相关机构</t>
         </is>
       </c>
       <c r="E193" t="n">
@@ -10661,7 +10666,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>副省级城市政协</t>
         </is>
       </c>
       <c r="E194" t="n">
@@ -10696,7 +10701,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>副省级城市政协</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -10731,7 +10736,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>副省级城市政协</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -10766,7 +10771,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>副省级城市政协</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -10801,7 +10806,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>副省级城市政协</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -10836,7 +10841,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>副省级城市政协</t>
         </is>
       </c>
       <c r="E199" t="n">
@@ -10871,7 +10876,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>副省级城市政协</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -10906,7 +10911,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>副省级城市政协</t>
         </is>
       </c>
       <c r="E201" t="n">
@@ -10941,7 +10946,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>副省级城市政协</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -10976,7 +10981,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>副省级城市政协</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -11011,7 +11016,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>副省级城市政协</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -11046,7 +11051,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -11081,7 +11086,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -11116,7 +11121,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -11151,7 +11156,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -11186,7 +11191,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -11221,7 +11226,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -11256,7 +11261,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -11291,7 +11296,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -11326,7 +11331,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E213" t="n">
@@ -11361,7 +11366,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E214" t="n">
@@ -11396,7 +11401,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E215" t="n">
@@ -11431,7 +11436,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E216" t="n">
@@ -11466,7 +11471,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E217" t="n">
@@ -11501,7 +11506,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -11536,7 +11541,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -11571,7 +11576,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -11606,7 +11611,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E221" t="n">
@@ -11641,7 +11646,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -11676,7 +11681,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -11711,7 +11716,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -11746,7 +11751,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E225" t="n">
@@ -11781,7 +11786,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E226" t="n">
@@ -11816,7 +11821,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -11851,7 +11856,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -11886,7 +11891,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -11921,7 +11926,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -11956,7 +11961,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -11991,7 +11996,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -12026,7 +12031,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E233" t="n">
@@ -12061,7 +12066,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E234" t="n">
@@ -12096,7 +12101,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E235" t="n">
@@ -12131,7 +12136,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E236" t="n">
@@ -12166,7 +12171,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E237" t="n">
@@ -12201,7 +12206,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -12236,7 +12241,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E239" t="n">
@@ -12271,7 +12276,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E240" t="n">
@@ -12306,7 +12311,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E241" t="n">
@@ -12341,7 +12346,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -12376,7 +12381,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E243" t="n">
@@ -12411,7 +12416,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E244" t="n">
@@ -12446,7 +12451,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E245" t="n">
@@ -12481,7 +12486,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -12516,7 +12521,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E247" t="n">
@@ -12551,7 +12556,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E248" t="n">
@@ -12586,7 +12591,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E249" t="n">
@@ -12621,7 +12626,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E250" t="n">
@@ -12656,7 +12661,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E251" t="n">
@@ -12691,7 +12696,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E252" t="n">
@@ -12726,7 +12731,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E253" t="n">
@@ -12761,7 +12766,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E254" t="n">
@@ -12796,7 +12801,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -12831,7 +12836,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E256" t="n">
@@ -12866,7 +12871,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E257" t="n">
@@ -12901,7 +12906,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -12936,7 +12941,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E259" t="n">
@@ -12971,7 +12976,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E260" t="n">
@@ -13006,7 +13011,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E261" t="n">
@@ -13041,7 +13046,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E262" t="n">
@@ -13076,7 +13081,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E263" t="n">
@@ -13111,7 +13116,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E264" t="n">
@@ -13146,7 +13151,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E265" t="n">
@@ -13181,7 +13186,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E266" t="n">
@@ -13216,7 +13221,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E267" t="n">
@@ -13251,7 +13256,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E268" t="n">
@@ -13286,7 +13291,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E269" t="n">
@@ -13321,7 +13326,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -13356,7 +13361,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E271" t="n">
@@ -13391,7 +13396,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E272" t="n">
@@ -13426,7 +13431,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E273" t="n">
@@ -13461,7 +13466,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E274" t="n">
@@ -13496,7 +13501,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E275" t="n">
@@ -13531,7 +13536,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E276" t="n">
@@ -13566,7 +13571,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E277" t="n">
@@ -13601,7 +13606,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E278" t="n">
@@ -13636,7 +13641,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E279" t="n">
@@ -13671,7 +13676,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E280" t="n">
@@ -13706,7 +13711,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E281" t="n">
@@ -13741,7 +13746,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E282" t="n">
@@ -13776,7 +13781,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E283" t="n">
@@ -13811,7 +13816,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E284" t="n">
@@ -13846,7 +13851,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E285" t="n">
@@ -13881,7 +13886,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -13916,7 +13921,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E287" t="n">
@@ -13951,7 +13956,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E288" t="n">
@@ -13986,7 +13991,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E289" t="n">
@@ -14021,7 +14026,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E290" t="n">
@@ -14056,7 +14061,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E291" t="n">
@@ -14091,7 +14096,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E292" t="n">
@@ -14126,7 +14131,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E293" t="n">
@@ -14161,7 +14166,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E294" t="n">
@@ -14196,7 +14201,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E295" t="n">
@@ -14231,7 +14236,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E296" t="n">
@@ -14266,7 +14271,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E297" t="n">
@@ -14301,7 +14306,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E298" t="n">
@@ -14336,7 +14341,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E299" t="n">
@@ -14371,7 +14376,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E300" t="n">
@@ -14406,7 +14411,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E301" t="n">
@@ -14441,7 +14446,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E302" t="n">
@@ -14476,7 +14481,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E303" t="n">
@@ -14511,7 +14516,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E304" t="n">
@@ -14546,7 +14551,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E305" t="n">
@@ -14581,7 +14586,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E306" t="n">
@@ -14616,7 +14621,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E307" t="n">
@@ -14651,7 +14656,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E308" t="n">
@@ -14686,7 +14691,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E309" t="n">
@@ -14721,7 +14726,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E310" t="n">
@@ -14756,7 +14761,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E311" t="n">
@@ -14791,7 +14796,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E312" t="n">
@@ -14826,7 +14831,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E313" t="n">
@@ -14861,7 +14866,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E314" t="n">
@@ -14896,7 +14901,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E315" t="n">
@@ -14931,7 +14936,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E316" t="n">
@@ -14966,7 +14971,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E317" t="n">
@@ -15001,7 +15006,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E318" t="n">
@@ -15036,7 +15041,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E319" t="n">
@@ -15071,7 +15076,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E320" t="n">
@@ -15106,7 +15111,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E321" t="n">
@@ -15141,7 +15146,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E322" t="n">
@@ -15176,7 +15181,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E323" t="n">
@@ -15211,7 +15216,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E324" t="n">
@@ -15246,7 +15251,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E325" t="n">
@@ -15281,7 +15286,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E326" t="n">
@@ -15316,7 +15321,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E327" t="n">
@@ -15351,7 +15356,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E328" t="n">
@@ -15386,7 +15391,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E329" t="n">
@@ -15421,7 +15426,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E330" t="n">
@@ -15456,7 +15461,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E331" t="n">
@@ -15491,7 +15496,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E332" t="n">
@@ -15526,7 +15531,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E333" t="n">
@@ -15561,7 +15566,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E334" t="n">
@@ -15596,7 +15601,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E335" t="n">
@@ -15631,7 +15636,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E336" t="n">
@@ -15666,7 +15671,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E337" t="n">
@@ -15701,7 +15706,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E338" t="n">
@@ -15736,7 +15741,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E339" t="n">
@@ -15771,7 +15776,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E340" t="n">
@@ -15806,7 +15811,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E341" t="n">
@@ -15841,7 +15846,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E342" t="n">
@@ -15876,7 +15881,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E343" t="n">
@@ -15911,7 +15916,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E344" t="n">
@@ -15946,7 +15951,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E345" t="n">
@@ -15981,7 +15986,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E346" t="n">
@@ -16016,7 +16021,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E347" t="n">
@@ -16051,7 +16056,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E348" t="n">
@@ -16086,7 +16091,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E349" t="n">
@@ -16121,7 +16126,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E350" t="n">
@@ -16156,7 +16161,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E351" t="n">
@@ -16191,7 +16196,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E352" t="n">
@@ -16226,7 +16231,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E353" t="n">
@@ -16261,7 +16266,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E354" t="n">
@@ -16296,7 +16301,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E355" t="n">
@@ -16331,7 +16336,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E356" t="n">
@@ -16366,7 +16371,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E357" t="n">
@@ -16401,7 +16406,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E358" t="n">
@@ -16436,7 +16441,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E359" t="n">
@@ -16471,7 +16476,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E360" t="n">
@@ -16506,7 +16511,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E361" t="n">
@@ -16541,7 +16546,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E362" t="n">
@@ -16576,7 +16581,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E363" t="n">
@@ -16611,7 +16616,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E364" t="n">
@@ -16646,7 +16651,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E365" t="n">
@@ -16681,7 +16686,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E366" t="n">
@@ -16716,7 +16721,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E367" t="n">
@@ -16751,7 +16756,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E368" t="n">
@@ -16786,7 +16791,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E369" t="n">
@@ -16821,7 +16826,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E370" t="n">
@@ -16856,7 +16861,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E371" t="n">
@@ -16891,7 +16896,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E372" t="n">
@@ -16926,7 +16931,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E373" t="n">
@@ -16961,7 +16966,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E374" t="n">
@@ -16996,7 +17001,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E375" t="n">
@@ -17031,7 +17036,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E376" t="n">
@@ -17066,7 +17071,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E377" t="n">
@@ -17101,7 +17106,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E378" t="n">
@@ -17136,7 +17141,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E379" t="n">
@@ -17171,7 +17176,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E380" t="n">
@@ -17206,7 +17211,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E381" t="n">
@@ -17241,7 +17246,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E382" t="n">
@@ -17276,7 +17281,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E383" t="n">
@@ -17311,7 +17316,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E384" t="n">
@@ -17346,7 +17351,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E385" t="n">
@@ -17381,7 +17386,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E386" t="n">
@@ -17416,7 +17421,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E387" t="n">
@@ -17451,7 +17456,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E388" t="n">
@@ -17486,7 +17491,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E389" t="n">
@@ -17521,7 +17526,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E390" t="n">
@@ -17556,7 +17561,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E391" t="n">
@@ -17591,7 +17596,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E392" t="n">
@@ -17626,7 +17631,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E393" t="n">
@@ -17661,7 +17666,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E394" t="n">
@@ -17696,7 +17701,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E395" t="n">
@@ -17731,7 +17736,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E396" t="n">
@@ -17766,7 +17771,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E397" t="n">
@@ -17801,7 +17806,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E398" t="n">
@@ -17836,7 +17841,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E399" t="n">
@@ -17871,7 +17876,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E400" t="n">
@@ -17906,7 +17911,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E401" t="n">
@@ -17941,7 +17946,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E402" t="n">
@@ -17976,7 +17981,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E403" t="n">
@@ -18011,7 +18016,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E404" t="n">
@@ -18046,7 +18051,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E405" t="n">
@@ -18081,7 +18086,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E406" t="n">
@@ -18116,7 +18121,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E407" t="n">
@@ -18151,7 +18156,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E408" t="n">
@@ -18186,7 +18191,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E409" t="n">
@@ -18221,7 +18226,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E410" t="n">
@@ -18256,7 +18261,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E411" t="n">
@@ -18291,7 +18296,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E412" t="n">
@@ -18326,7 +18331,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E413" t="n">
@@ -18361,7 +18366,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E414" t="n">
@@ -18396,7 +18401,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E415" t="n">
@@ -18431,7 +18436,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E416" t="n">
@@ -18466,7 +18471,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E417" t="n">
@@ -18501,7 +18506,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E418" t="n">
@@ -18536,7 +18541,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E419" t="n">
@@ -18571,7 +18576,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E420" t="n">
@@ -18606,7 +18611,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E421" t="n">
@@ -18641,7 +18646,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E422" t="n">
@@ -18676,7 +18681,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E423" t="n">
@@ -18711,7 +18716,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E424" t="n">
@@ -18746,7 +18751,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E425" t="n">
@@ -18781,7 +18786,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E426" t="n">
@@ -18816,7 +18821,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E427" t="n">
@@ -18851,7 +18856,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E428" t="n">
@@ -18886,7 +18891,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E429" t="n">
@@ -18921,7 +18926,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E430" t="n">
@@ -18956,7 +18961,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E431" t="n">
@@ -18991,7 +18996,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E432" t="n">
@@ -19026,7 +19031,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E433" t="n">
@@ -19061,7 +19066,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E434" t="n">
@@ -19096,7 +19101,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E435" t="n">
@@ -19131,7 +19136,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E436" t="n">
@@ -19166,7 +19171,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E437" t="n">
@@ -19201,7 +19206,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E438" t="n">
@@ -19236,7 +19241,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E439" t="n">
@@ -19271,7 +19276,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E440" t="n">
@@ -19306,7 +19311,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E441" t="n">
@@ -19341,7 +19346,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E442" t="n">
@@ -19376,7 +19381,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E443" t="n">
@@ -19411,7 +19416,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E444" t="n">
@@ -19446,7 +19451,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E445" t="n">
@@ -19481,7 +19486,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E446" t="n">
@@ -19516,7 +19521,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E447" t="n">
@@ -19551,7 +19556,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E448" t="n">
@@ -19586,7 +19591,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E449" t="n">
@@ -19621,7 +19626,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E450" t="n">
@@ -19656,7 +19661,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E451" t="n">
@@ -19691,7 +19696,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E452" t="n">
@@ -19726,7 +19731,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E453" t="n">
@@ -19761,7 +19766,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E454" t="n">
@@ -19796,7 +19801,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E455" t="n">
@@ -19831,7 +19836,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E456" t="n">
@@ -19866,7 +19871,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E457" t="n">
@@ -19901,7 +19906,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E458" t="n">
@@ -19936,7 +19941,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E459" t="n">
@@ -19971,7 +19976,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E460" t="n">
@@ -20006,7 +20011,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E461" t="n">
@@ -20041,7 +20046,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E462" t="n">
@@ -20076,7 +20081,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E463" t="n">
@@ -20111,7 +20116,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E464" t="n">
